--- a/thesis/evidencing/ADS&AI Work Log Graduation Project.xlsx
+++ b/thesis/evidencing/ADS&AI Work Log Graduation Project.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="520">
   <si>
     <t>Date</t>
   </si>
@@ -353,36 +353,24 @@
     <t>Auditability over accuracy</t>
   </si>
   <si>
-    <t>thesis 2.3</t>
-  </si>
-  <si>
     <t>Finalise H1-H4 wording</t>
   </si>
   <si>
     <t>From proposal feedback</t>
   </si>
   <si>
-    <t>PROJECT_CONTEXT.md</t>
-  </si>
-  <si>
     <t>Plan src/ structure and config approach</t>
   </si>
   <si>
     <t>Folder conventions, config pattern</t>
   </si>
   <si>
-    <t>config/</t>
-  </si>
-  <si>
     <t>Download RDD2022, verify folders/counts</t>
   </si>
   <si>
     <t>7 country sources</t>
   </si>
   <si>
-    <t>data/raw/</t>
-  </si>
-  <si>
     <t>Explore class/country distribution in notebook</t>
   </si>
   <si>
@@ -413,9 +401,6 @@
     <t>First dataset scale, for pipeline validation</t>
   </si>
   <si>
-    <t>data/processed/small/</t>
-  </si>
-  <si>
     <t>Verify small dataset integrity</t>
   </si>
   <si>
@@ -452,9 +437,6 @@
     <t>Image size, batch, early stop</t>
   </si>
   <si>
-    <t>configs/</t>
-  </si>
-  <si>
     <t>Write Faster R-CNN training config</t>
   </si>
   <si>
@@ -1629,6 +1611,21 @@
   </si>
   <si>
     <t>I demoed the app to the supervisor and got feedback that everything works fine by now, but have to ellaborate everything in the thesis.</t>
+  </si>
+  <si>
+    <t>visual dataset inspection notebook</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>scripts</t>
+  </si>
+  <si>
+    <t>first YOLO training</t>
+  </si>
+  <si>
+    <t>first FasteRNN training</t>
   </si>
 </sst>
 </file>
@@ -1639,7 +1636,7 @@
     <numFmt numFmtId="164" formatCode="d&quot;-&quot;mmm&quot;-&quot;yyyy"/>
     <numFmt numFmtId="165" formatCode="d/m/yy"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1749,6 +1746,12 @@
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="15">
@@ -1951,10 +1954,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2075,37 +2079,17 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2119,14 +2103,23 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2140,10 +2133,21 @@
     <xf numFmtId="0" fontId="7" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2151,8 +2155,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="70">
@@ -3129,53 +3135,53 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
     </row>
     <row r="3" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="69" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="54"/>
     </row>
     <row r="4" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="69" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="52" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="54"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="46">
@@ -3206,7 +3212,7 @@
         <f t="shared" ref="I5:I13" si="0">H5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="44" t="s">
+      <c r="J5" s="82" t="s">
         <v>81</v>
       </c>
       <c r="K5" s="24"/>
@@ -3240,7 +3246,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J6" s="44" t="s">
+      <c r="J6" s="82" t="s">
         <v>84</v>
       </c>
       <c r="K6" s="13"/>
@@ -3274,7 +3280,7 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="J7" s="44" t="s">
+      <c r="J7" s="82" t="s">
         <v>87</v>
       </c>
       <c r="K7" s="13"/>
@@ -3308,7 +3314,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="44" t="s">
+      <c r="J8" s="82" t="s">
         <v>87</v>
       </c>
       <c r="K8" s="13"/>
@@ -3342,7 +3348,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="44" t="s">
+      <c r="J9" s="82" t="s">
         <v>92</v>
       </c>
       <c r="K9" s="13"/>
@@ -3376,8 +3382,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="44" t="s">
-        <v>95</v>
+      <c r="J10" s="82" t="s">
+        <v>92</v>
       </c>
       <c r="K10" s="13"/>
     </row>
@@ -3389,10 +3395,10 @@
         <v>59</v>
       </c>
       <c r="C11" s="48" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="E11" s="39" t="s">
         <v>66</v>
@@ -3421,10 +3427,10 @@
         <v>59</v>
       </c>
       <c r="C12" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="44" t="s">
         <v>96</v>
-      </c>
-      <c r="D12" s="44" t="s">
-        <v>97</v>
       </c>
       <c r="E12" s="44" t="s">
         <v>48</v>
@@ -3442,9 +3448,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="44" t="s">
-        <v>98</v>
-      </c>
+      <c r="J12" s="44"/>
       <c r="K12" s="13"/>
     </row>
     <row r="13" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -3455,10 +3459,10 @@
         <v>59</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E13" s="44" t="s">
         <v>66</v>
@@ -3476,9 +3480,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="44" t="s">
-        <v>101</v>
-      </c>
+      <c r="J13" s="44"/>
       <c r="K13" s="13"/>
     </row>
     <row r="14" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -3506,53 +3508,53 @@
       <c r="K14" s="18"/>
     </row>
     <row r="15" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="70" t="s">
+      <c r="A15" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="56"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="56"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="52"/>
+      <c r="B16" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="54"/>
     </row>
     <row r="17" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="52"/>
+      <c r="B17" s="56" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="54"/>
     </row>
     <row r="18" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="46">
@@ -3562,10 +3564,10 @@
         <v>59</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E18" s="44" t="s">
         <v>57</v>
@@ -3583,8 +3585,8 @@
         <f t="shared" ref="I18:I25" si="2">H18-G18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="44" t="s">
-        <v>104</v>
+      <c r="J18" s="82" t="s">
+        <v>516</v>
       </c>
       <c r="K18" s="24"/>
     </row>
@@ -3596,10 +3598,10 @@
         <v>59</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D19" s="44" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E19" s="44" t="s">
         <v>57</v>
@@ -3617,8 +3619,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="44" t="s">
-        <v>107</v>
+      <c r="J19" s="82" t="s">
+        <v>515</v>
       </c>
       <c r="K19" s="24"/>
     </row>
@@ -3630,10 +3632,10 @@
         <v>59</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D20" s="44" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E20" s="44" t="s">
         <v>48</v>
@@ -3651,8 +3653,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="44" t="s">
-        <v>110</v>
+      <c r="J20" s="82" t="s">
+        <v>106</v>
       </c>
       <c r="K20" s="24"/>
     </row>
@@ -3664,10 +3666,10 @@
         <v>59</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E21" s="44" t="s">
         <v>54</v>
@@ -3685,8 +3687,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="44" t="s">
-        <v>110</v>
+      <c r="J21" s="82" t="s">
+        <v>106</v>
       </c>
       <c r="K21" s="24"/>
     </row>
@@ -3698,10 +3700,10 @@
         <v>59</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E22" s="44" t="s">
         <v>54</v>
@@ -3719,8 +3721,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J22" s="44" t="s">
-        <v>115</v>
+      <c r="J22" s="82" t="s">
+        <v>516</v>
       </c>
       <c r="K22" s="24"/>
     </row>
@@ -3732,10 +3734,10 @@
         <v>59</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E23" s="44" t="s">
         <v>60</v>
@@ -3753,8 +3755,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J23" s="44" t="s">
-        <v>110</v>
+      <c r="J23" s="82" t="s">
+        <v>517</v>
       </c>
       <c r="K23" s="24"/>
     </row>
@@ -3766,10 +3768,10 @@
         <v>59</v>
       </c>
       <c r="C24" s="43" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E24" s="44" t="s">
         <v>74</v>
@@ -3798,10 +3800,10 @@
         <v>59</v>
       </c>
       <c r="C25" s="43" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E25" s="44" t="s">
         <v>66</v>
@@ -3847,53 +3849,53 @@
       <c r="K26" s="18"/>
     </row>
     <row r="27" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="65" t="s">
+      <c r="A27" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="51"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51"/>
-      <c r="K27" s="52"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="54"/>
     </row>
     <row r="28" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="66" t="s">
-        <v>146</v>
-      </c>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="51"/>
-      <c r="K28" s="52"/>
+      <c r="B28" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="66" t="s">
-        <v>147</v>
-      </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
-      <c r="K29" s="52"/>
+      <c r="B29" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="54"/>
     </row>
     <row r="30" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="46">
@@ -3903,10 +3905,10 @@
         <v>59</v>
       </c>
       <c r="C30" s="43" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D30" s="44" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E30" s="44" t="s">
         <v>54</v>
@@ -3924,8 +3926,8 @@
         <f t="shared" ref="I30:I37" si="4">H30-G30</f>
         <v>0</v>
       </c>
-      <c r="J30" s="44" t="s">
-        <v>128</v>
+      <c r="J30" s="82" t="s">
+        <v>518</v>
       </c>
       <c r="K30" s="24"/>
     </row>
@@ -3937,10 +3939,10 @@
         <v>59</v>
       </c>
       <c r="C31" s="43" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D31" s="44" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E31" s="44" t="s">
         <v>54</v>
@@ -3958,8 +3960,8 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J31" s="44" t="s">
-        <v>128</v>
+      <c r="J31" s="82" t="s">
+        <v>518</v>
       </c>
       <c r="K31" s="24"/>
     </row>
@@ -3971,16 +3973,16 @@
         <v>59</v>
       </c>
       <c r="C32" s="43" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D32" s="44" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E32" s="44" t="s">
         <v>70</v>
       </c>
       <c r="F32" s="44" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G32" s="44">
         <v>2</v>
@@ -3992,8 +3994,8 @@
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
-      <c r="J32" s="44" t="s">
-        <v>107</v>
+      <c r="J32" s="82" t="s">
+        <v>519</v>
       </c>
       <c r="K32" s="24"/>
     </row>
@@ -4005,10 +4007,10 @@
         <v>59</v>
       </c>
       <c r="C33" s="43" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D33" s="44" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E33" s="44" t="s">
         <v>54</v>
@@ -4026,8 +4028,8 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J33" s="44" t="s">
-        <v>136</v>
+      <c r="J33" s="82" t="s">
+        <v>518</v>
       </c>
       <c r="K33" s="24"/>
     </row>
@@ -4039,10 +4041,10 @@
         <v>59</v>
       </c>
       <c r="C34" s="43" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D34" s="44" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E34" s="44" t="s">
         <v>54</v>
@@ -4060,8 +4062,8 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J34" s="44" t="s">
-        <v>136</v>
+      <c r="J34" s="82" t="s">
+        <v>519</v>
       </c>
       <c r="K34" s="24"/>
     </row>
@@ -4073,10 +4075,10 @@
         <v>59</v>
       </c>
       <c r="C35" s="43" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D35" s="44" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E35" s="44" t="s">
         <v>60</v>
@@ -4095,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="44" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K35" s="24"/>
     </row>
@@ -4107,10 +4109,10 @@
         <v>59</v>
       </c>
       <c r="C36" s="43" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D36" s="44" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E36" s="44" t="s">
         <v>74</v>
@@ -4139,10 +4141,10 @@
         <v>59</v>
       </c>
       <c r="C37" s="43" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E37" s="44" t="s">
         <v>48</v>
@@ -4161,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="44" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="K37" s="24"/>
     </row>
@@ -4190,53 +4192,53 @@
       <c r="K38" s="18"/>
     </row>
     <row r="39" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="67" t="s">
+      <c r="A39" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="51"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="51"/>
-      <c r="K39" s="52"/>
+      <c r="B39" s="53"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="54"/>
     </row>
     <row r="40" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B40" s="61" t="s">
-        <v>148</v>
-      </c>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="51"/>
-      <c r="J40" s="51"/>
-      <c r="K40" s="52"/>
+      <c r="B40" s="60" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="53"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="54"/>
     </row>
     <row r="41" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="61" t="s">
-        <v>149</v>
-      </c>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="51"/>
-      <c r="I41" s="51"/>
-      <c r="J41" s="51"/>
-      <c r="K41" s="52"/>
+      <c r="B41" s="60" t="s">
+        <v>143</v>
+      </c>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53"/>
+      <c r="H41" s="53"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="54"/>
     </row>
     <row r="42" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="46">
@@ -4246,10 +4248,10 @@
         <v>59</v>
       </c>
       <c r="C42" s="43" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D42" s="44" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E42" s="44" t="s">
         <v>48</v>
@@ -4268,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="44" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="K42" s="24"/>
     </row>
@@ -4280,10 +4282,10 @@
         <v>59</v>
       </c>
       <c r="C43" s="43" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D43" s="44" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E43" s="44" t="s">
         <v>48</v>
@@ -4302,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="44" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="K43" s="24"/>
     </row>
@@ -4314,10 +4316,10 @@
         <v>59</v>
       </c>
       <c r="C44" s="43" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D44" s="44" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E44" s="44" t="s">
         <v>48</v>
@@ -4336,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="44" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="K44" s="24"/>
     </row>
@@ -4348,10 +4350,10 @@
         <v>59</v>
       </c>
       <c r="C45" s="43" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D45" s="44" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E45" s="44" t="s">
         <v>57</v>
@@ -4370,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="44" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="K45" s="24"/>
     </row>
@@ -4382,10 +4384,10 @@
         <v>59</v>
       </c>
       <c r="C46" s="48" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D46" s="44" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E46" s="39" t="s">
         <v>66</v>
@@ -4414,10 +4416,10 @@
         <v>59</v>
       </c>
       <c r="C47" s="43" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D47" s="44" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E47" s="44" t="s">
         <v>54</v>
@@ -4436,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="44" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="K47" s="24"/>
     </row>
@@ -4448,10 +4450,10 @@
         <v>59</v>
       </c>
       <c r="C48" s="43" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D48" s="44" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E48" s="44" t="s">
         <v>54</v>
@@ -4470,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="44" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="K48" s="24"/>
     </row>
@@ -4482,10 +4484,10 @@
         <v>59</v>
       </c>
       <c r="C49" s="43" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E49" s="44" t="s">
         <v>54</v>
@@ -4504,7 +4506,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="44" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="K49" s="24"/>
     </row>
@@ -4516,10 +4518,10 @@
         <v>59</v>
       </c>
       <c r="C50" s="43" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E50" s="44" t="s">
         <v>60</v>
@@ -4538,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="44" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="K50" s="24"/>
     </row>
@@ -4567,53 +4569,53 @@
       <c r="K51" s="18"/>
     </row>
     <row r="52" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="62" t="s">
+      <c r="A52" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="B52" s="51"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="51"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="51"/>
-      <c r="G52" s="51"/>
-      <c r="H52" s="51"/>
-      <c r="I52" s="51"/>
-      <c r="J52" s="51"/>
-      <c r="K52" s="52"/>
+      <c r="B52" s="53"/>
+      <c r="C52" s="53"/>
+      <c r="D52" s="53"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53"/>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="54"/>
     </row>
     <row r="53" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B53" s="63" t="s">
-        <v>170</v>
-      </c>
-      <c r="C53" s="77"/>
-      <c r="D53" s="77"/>
-      <c r="E53" s="77"/>
-      <c r="F53" s="77"/>
-      <c r="G53" s="77"/>
-      <c r="H53" s="77"/>
-      <c r="I53" s="77"/>
-      <c r="J53" s="77"/>
-      <c r="K53" s="78"/>
+      <c r="B53" s="62" t="s">
+        <v>164</v>
+      </c>
+      <c r="C53" s="63"/>
+      <c r="D53" s="63"/>
+      <c r="E53" s="63"/>
+      <c r="F53" s="63"/>
+      <c r="G53" s="63"/>
+      <c r="H53" s="63"/>
+      <c r="I53" s="63"/>
+      <c r="J53" s="63"/>
+      <c r="K53" s="64"/>
     </row>
     <row r="54" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="B54" s="63" t="s">
-        <v>171</v>
-      </c>
-      <c r="C54" s="77"/>
-      <c r="D54" s="77"/>
-      <c r="E54" s="77"/>
-      <c r="F54" s="77"/>
-      <c r="G54" s="77"/>
-      <c r="H54" s="77"/>
-      <c r="I54" s="77"/>
-      <c r="J54" s="77"/>
-      <c r="K54" s="78"/>
+      <c r="B54" s="62" t="s">
+        <v>165</v>
+      </c>
+      <c r="C54" s="63"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="63"/>
+      <c r="F54" s="63"/>
+      <c r="G54" s="63"/>
+      <c r="H54" s="63"/>
+      <c r="I54" s="63"/>
+      <c r="J54" s="63"/>
+      <c r="K54" s="64"/>
     </row>
     <row r="55" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="46">
@@ -4623,10 +4625,10 @@
         <v>59</v>
       </c>
       <c r="C55" s="43" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D55" s="44" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E55" s="44" t="s">
         <v>54</v>
@@ -4645,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="44" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="K55" s="24"/>
     </row>
@@ -4657,10 +4659,10 @@
         <v>59</v>
       </c>
       <c r="C56" s="43" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D56" s="44" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E56" s="44" t="s">
         <v>54</v>
@@ -4679,7 +4681,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="44" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="K56" s="24"/>
     </row>
@@ -4691,10 +4693,10 @@
         <v>59</v>
       </c>
       <c r="C57" s="43" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D57" s="44" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E57" s="44" t="s">
         <v>54</v>
@@ -4713,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="44" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="K57" s="24"/>
     </row>
@@ -4725,10 +4727,10 @@
         <v>59</v>
       </c>
       <c r="C58" s="43" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D58" s="44" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E58" s="44" t="s">
         <v>54</v>
@@ -4747,7 +4749,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="44" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="K58" s="24"/>
     </row>
@@ -4759,10 +4761,10 @@
         <v>59</v>
       </c>
       <c r="C59" s="43" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D59" s="44" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E59" s="44" t="s">
         <v>54</v>
@@ -4781,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="44" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="K59" s="24"/>
     </row>
@@ -4793,10 +4795,10 @@
         <v>59</v>
       </c>
       <c r="C60" s="43" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D60" s="44" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E60" s="44" t="s">
         <v>60</v>
@@ -4815,7 +4817,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="44" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="K60" s="24"/>
     </row>
@@ -4827,10 +4829,10 @@
         <v>59</v>
       </c>
       <c r="C61" s="43" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D61" s="44" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E61" s="44" t="s">
         <v>60</v>
@@ -4859,10 +4861,10 @@
         <v>59</v>
       </c>
       <c r="C62" s="43" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D62" s="44" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E62" s="44" t="s">
         <v>57</v>
@@ -4881,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="44" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="K62" s="24"/>
     </row>
@@ -4910,53 +4912,53 @@
       <c r="K63" s="18"/>
     </row>
     <row r="64" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="60" t="s">
+      <c r="A64" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="B64" s="51"/>
-      <c r="C64" s="51"/>
-      <c r="D64" s="51"/>
-      <c r="E64" s="51"/>
-      <c r="F64" s="51"/>
-      <c r="G64" s="51"/>
-      <c r="H64" s="51"/>
-      <c r="I64" s="51"/>
-      <c r="J64" s="51"/>
-      <c r="K64" s="52"/>
+      <c r="B64" s="53"/>
+      <c r="C64" s="53"/>
+      <c r="D64" s="53"/>
+      <c r="E64" s="53"/>
+      <c r="F64" s="53"/>
+      <c r="G64" s="53"/>
+      <c r="H64" s="53"/>
+      <c r="I64" s="53"/>
+      <c r="J64" s="53"/>
+      <c r="K64" s="54"/>
     </row>
     <row r="65" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B65" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="C65" s="51"/>
-      <c r="D65" s="51"/>
-      <c r="E65" s="51"/>
-      <c r="F65" s="51"/>
-      <c r="G65" s="51"/>
-      <c r="H65" s="51"/>
-      <c r="I65" s="51"/>
-      <c r="J65" s="51"/>
-      <c r="K65" s="52"/>
+      <c r="B65" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="C65" s="53"/>
+      <c r="D65" s="53"/>
+      <c r="E65" s="53"/>
+      <c r="F65" s="53"/>
+      <c r="G65" s="53"/>
+      <c r="H65" s="53"/>
+      <c r="I65" s="53"/>
+      <c r="J65" s="53"/>
+      <c r="K65" s="54"/>
     </row>
     <row r="66" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B66" s="53" t="s">
-        <v>194</v>
-      </c>
-      <c r="C66" s="51"/>
-      <c r="D66" s="51"/>
-      <c r="E66" s="51"/>
-      <c r="F66" s="51"/>
-      <c r="G66" s="51"/>
-      <c r="H66" s="51"/>
-      <c r="I66" s="51"/>
-      <c r="J66" s="51"/>
-      <c r="K66" s="52"/>
+      <c r="B66" s="73" t="s">
+        <v>188</v>
+      </c>
+      <c r="C66" s="53"/>
+      <c r="D66" s="53"/>
+      <c r="E66" s="53"/>
+      <c r="F66" s="53"/>
+      <c r="G66" s="53"/>
+      <c r="H66" s="53"/>
+      <c r="I66" s="53"/>
+      <c r="J66" s="53"/>
+      <c r="K66" s="54"/>
     </row>
     <row r="67" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="46">
@@ -4966,10 +4968,10 @@
         <v>59</v>
       </c>
       <c r="C67" s="43" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D67" s="44" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E67" s="44" t="s">
         <v>54</v>
@@ -4988,7 +4990,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="44" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K67" s="47"/>
     </row>
@@ -5000,10 +5002,10 @@
         <v>59</v>
       </c>
       <c r="C68" s="43" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D68" s="44" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="E68" s="44" t="s">
         <v>54</v>
@@ -5022,7 +5024,7 @@
         <v>0</v>
       </c>
       <c r="J68" s="44" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K68" s="47"/>
     </row>
@@ -5034,10 +5036,10 @@
         <v>59</v>
       </c>
       <c r="C69" s="43" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D69" s="44" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E69" s="44" t="s">
         <v>48</v>
@@ -5056,7 +5058,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="44" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="K69" s="47"/>
     </row>
@@ -5068,10 +5070,10 @@
         <v>59</v>
       </c>
       <c r="C70" s="43" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D70" s="44" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E70" s="44" t="s">
         <v>54</v>
@@ -5090,7 +5092,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="44" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="K70" s="47"/>
     </row>
@@ -5102,10 +5104,10 @@
         <v>59</v>
       </c>
       <c r="C71" s="48" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D71" s="39" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="E71" s="39" t="s">
         <v>66</v>
@@ -5134,10 +5136,10 @@
         <v>59</v>
       </c>
       <c r="C72" s="43" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D72" s="44" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E72" s="44" t="s">
         <v>54</v>
@@ -5156,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="44" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="K72" s="47"/>
     </row>
@@ -5168,10 +5170,10 @@
         <v>59</v>
       </c>
       <c r="C73" s="43" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D73" s="44" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E73" s="44" t="s">
         <v>54</v>
@@ -5190,7 +5192,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="44" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="K73" s="47"/>
     </row>
@@ -5202,10 +5204,10 @@
         <v>59</v>
       </c>
       <c r="C74" s="43" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D74" s="44" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E74" s="44" t="s">
         <v>60</v>
@@ -5225,7 +5227,7 @@
       </c>
       <c r="J74" s="44"/>
       <c r="K74" s="47" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -5236,10 +5238,10 @@
         <v>59</v>
       </c>
       <c r="C75" s="43" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D75" s="44" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E75" s="44" t="s">
         <v>70</v>
@@ -5285,53 +5287,53 @@
       <c r="K76" s="18"/>
     </row>
     <row r="77" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="59" t="s">
+      <c r="A77" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B77" s="51"/>
-      <c r="C77" s="51"/>
-      <c r="D77" s="51"/>
-      <c r="E77" s="51"/>
-      <c r="F77" s="51"/>
-      <c r="G77" s="51"/>
-      <c r="H77" s="51"/>
-      <c r="I77" s="51"/>
-      <c r="J77" s="51"/>
-      <c r="K77" s="52"/>
+      <c r="B77" s="53"/>
+      <c r="C77" s="53"/>
+      <c r="D77" s="53"/>
+      <c r="E77" s="53"/>
+      <c r="F77" s="53"/>
+      <c r="G77" s="53"/>
+      <c r="H77" s="53"/>
+      <c r="I77" s="53"/>
+      <c r="J77" s="53"/>
+      <c r="K77" s="54"/>
     </row>
     <row r="78" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B78" s="50" t="s">
-        <v>218</v>
-      </c>
-      <c r="C78" s="51"/>
-      <c r="D78" s="51"/>
-      <c r="E78" s="51"/>
-      <c r="F78" s="51"/>
-      <c r="G78" s="51"/>
-      <c r="H78" s="51"/>
-      <c r="I78" s="51"/>
-      <c r="J78" s="51"/>
-      <c r="K78" s="52"/>
+      <c r="B78" s="75" t="s">
+        <v>212</v>
+      </c>
+      <c r="C78" s="53"/>
+      <c r="D78" s="53"/>
+      <c r="E78" s="53"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53"/>
+      <c r="H78" s="53"/>
+      <c r="I78" s="53"/>
+      <c r="J78" s="53"/>
+      <c r="K78" s="54"/>
     </row>
     <row r="79" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B79" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="C79" s="51"/>
-      <c r="D79" s="51"/>
-      <c r="E79" s="51"/>
-      <c r="F79" s="51"/>
-      <c r="G79" s="51"/>
-      <c r="H79" s="51"/>
-      <c r="I79" s="51"/>
-      <c r="J79" s="51"/>
-      <c r="K79" s="52"/>
+      <c r="B79" s="75" t="s">
+        <v>213</v>
+      </c>
+      <c r="C79" s="53"/>
+      <c r="D79" s="53"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
+      <c r="H79" s="53"/>
+      <c r="I79" s="53"/>
+      <c r="J79" s="53"/>
+      <c r="K79" s="54"/>
     </row>
     <row r="80" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="46">
@@ -5341,10 +5343,10 @@
         <v>59</v>
       </c>
       <c r="C80" s="43" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D80" s="44" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="E80" s="44" t="s">
         <v>57</v>
@@ -5363,7 +5365,7 @@
         <v>0</v>
       </c>
       <c r="J80" s="44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K80" s="47"/>
     </row>
@@ -5375,10 +5377,10 @@
         <v>59</v>
       </c>
       <c r="C81" s="43" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D81" s="44" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E81" s="44" t="s">
         <v>57</v>
@@ -5397,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K81" s="47"/>
     </row>
@@ -5409,16 +5411,16 @@
         <v>59</v>
       </c>
       <c r="C82" s="43" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D82" s="44" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E82" s="44" t="s">
         <v>57</v>
       </c>
       <c r="F82" s="44" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G82" s="44">
         <v>1.5</v>
@@ -5431,10 +5433,10 @@
         <v>0</v>
       </c>
       <c r="J82" s="44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K82" s="47" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -5445,16 +5447,16 @@
         <v>59</v>
       </c>
       <c r="C83" s="43" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D83" s="44" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E83" s="44" t="s">
         <v>57</v>
       </c>
       <c r="F83" s="44" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G83" s="44">
         <v>1.5</v>
@@ -5467,10 +5469,10 @@
         <v>0</v>
       </c>
       <c r="J83" s="44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K83" s="47" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -5481,10 +5483,10 @@
         <v>59</v>
       </c>
       <c r="C84" s="43" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D84" s="44" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E84" s="44" t="s">
         <v>54</v>
@@ -5503,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="44" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="K84" s="47"/>
     </row>
@@ -5515,10 +5517,10 @@
         <v>59</v>
       </c>
       <c r="C85" s="43" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D85" s="44" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="E85" s="44" t="s">
         <v>54</v>
@@ -5537,7 +5539,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="44" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="K85" s="47"/>
     </row>
@@ -5549,10 +5551,10 @@
         <v>59</v>
       </c>
       <c r="C86" s="43" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D86" s="44" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="E86" s="44" t="s">
         <v>54</v>
@@ -5571,7 +5573,7 @@
         <v>0.5</v>
       </c>
       <c r="J86" s="44" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="K86" s="47"/>
     </row>
@@ -5583,10 +5585,10 @@
         <v>59</v>
       </c>
       <c r="C87" s="43" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D87" s="44" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E87" s="44" t="s">
         <v>60</v>
@@ -5605,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="J87" s="44" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K87" s="47"/>
     </row>
@@ -5634,53 +5636,53 @@
       <c r="K88" s="18"/>
     </row>
     <row r="89" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A89" s="54" t="s">
+      <c r="A89" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="B89" s="51"/>
-      <c r="C89" s="51"/>
-      <c r="D89" s="51"/>
-      <c r="E89" s="51"/>
-      <c r="F89" s="51"/>
-      <c r="G89" s="51"/>
-      <c r="H89" s="51"/>
-      <c r="I89" s="51"/>
-      <c r="J89" s="51"/>
-      <c r="K89" s="52"/>
+      <c r="B89" s="53"/>
+      <c r="C89" s="53"/>
+      <c r="D89" s="53"/>
+      <c r="E89" s="53"/>
+      <c r="F89" s="53"/>
+      <c r="G89" s="53"/>
+      <c r="H89" s="53"/>
+      <c r="I89" s="53"/>
+      <c r="J89" s="53"/>
+      <c r="K89" s="54"/>
     </row>
     <row r="90" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B90" s="71" t="s">
-        <v>236</v>
-      </c>
-      <c r="C90" s="72"/>
-      <c r="D90" s="72"/>
-      <c r="E90" s="72"/>
-      <c r="F90" s="72"/>
-      <c r="G90" s="72"/>
-      <c r="H90" s="72"/>
-      <c r="I90" s="72"/>
-      <c r="J90" s="72"/>
-      <c r="K90" s="73"/>
+      <c r="B90" s="66" t="s">
+        <v>230</v>
+      </c>
+      <c r="C90" s="67"/>
+      <c r="D90" s="67"/>
+      <c r="E90" s="67"/>
+      <c r="F90" s="67"/>
+      <c r="G90" s="67"/>
+      <c r="H90" s="67"/>
+      <c r="I90" s="67"/>
+      <c r="J90" s="67"/>
+      <c r="K90" s="68"/>
     </row>
     <row r="91" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="B91" s="74" t="s">
-        <v>237</v>
-      </c>
-      <c r="C91" s="75"/>
-      <c r="D91" s="75"/>
-      <c r="E91" s="75"/>
-      <c r="F91" s="75"/>
-      <c r="G91" s="75"/>
-      <c r="H91" s="75"/>
-      <c r="I91" s="75"/>
-      <c r="J91" s="75"/>
-      <c r="K91" s="76"/>
+      <c r="B91" s="69" t="s">
+        <v>231</v>
+      </c>
+      <c r="C91" s="70"/>
+      <c r="D91" s="70"/>
+      <c r="E91" s="70"/>
+      <c r="F91" s="70"/>
+      <c r="G91" s="70"/>
+      <c r="H91" s="70"/>
+      <c r="I91" s="70"/>
+      <c r="J91" s="70"/>
+      <c r="K91" s="71"/>
     </row>
     <row r="92" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="46">
@@ -5690,10 +5692,10 @@
         <v>59</v>
       </c>
       <c r="C92" s="43" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D92" s="44" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E92" s="44" t="s">
         <v>48</v>
@@ -5712,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="44" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K92" s="24"/>
     </row>
@@ -5724,10 +5726,10 @@
         <v>59</v>
       </c>
       <c r="C93" s="43" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D93" s="44" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E93" s="44" t="s">
         <v>54</v>
@@ -5746,7 +5748,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="44" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K93" s="24"/>
     </row>
@@ -5758,10 +5760,10 @@
         <v>59</v>
       </c>
       <c r="C94" s="43" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D94" s="44" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E94" s="44" t="s">
         <v>54</v>
@@ -5780,7 +5782,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="44" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K94" s="24"/>
     </row>
@@ -5792,10 +5794,10 @@
         <v>59</v>
       </c>
       <c r="C95" s="43" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D95" s="44" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E95" s="44" t="s">
         <v>60</v>
@@ -5814,7 +5816,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="44" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K95" s="24"/>
     </row>
@@ -5826,10 +5828,10 @@
         <v>59</v>
       </c>
       <c r="C96" s="43" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D96" s="44" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E96" s="44" t="s">
         <v>54</v>
@@ -5848,7 +5850,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="44" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K96" s="24"/>
     </row>
@@ -5860,10 +5862,10 @@
         <v>59</v>
       </c>
       <c r="C97" s="43" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D97" s="44" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="E97" s="44" t="s">
         <v>60</v>
@@ -5882,7 +5884,7 @@
         <v>0</v>
       </c>
       <c r="J97" s="44" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="K97" s="24"/>
     </row>
@@ -5894,10 +5896,10 @@
         <v>59</v>
       </c>
       <c r="C98" s="43" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D98" s="44" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E98" s="44" t="s">
         <v>54</v>
@@ -5916,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="44" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K98" s="24"/>
     </row>
@@ -5950,53 +5952,53 @@
       <c r="I100" s="25"/>
     </row>
     <row r="102" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="68" t="s">
+      <c r="A102" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="B102" s="56"/>
-      <c r="C102" s="56"/>
-      <c r="D102" s="56"/>
-      <c r="E102" s="56"/>
-      <c r="F102" s="56"/>
-      <c r="G102" s="56"/>
-      <c r="H102" s="56"/>
-      <c r="I102" s="56"/>
-      <c r="J102" s="56"/>
-      <c r="K102" s="56"/>
+      <c r="B102" s="51"/>
+      <c r="C102" s="51"/>
+      <c r="D102" s="51"/>
+      <c r="E102" s="51"/>
+      <c r="F102" s="51"/>
+      <c r="G102" s="51"/>
+      <c r="H102" s="51"/>
+      <c r="I102" s="51"/>
+      <c r="J102" s="51"/>
+      <c r="K102" s="51"/>
     </row>
     <row r="103" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B103" s="69" t="s">
-        <v>254</v>
-      </c>
-      <c r="C103" s="51"/>
-      <c r="D103" s="51"/>
-      <c r="E103" s="51"/>
-      <c r="F103" s="51"/>
-      <c r="G103" s="51"/>
-      <c r="H103" s="51"/>
-      <c r="I103" s="51"/>
-      <c r="J103" s="51"/>
-      <c r="K103" s="52"/>
+      <c r="B103" s="52" t="s">
+        <v>248</v>
+      </c>
+      <c r="C103" s="53"/>
+      <c r="D103" s="53"/>
+      <c r="E103" s="53"/>
+      <c r="F103" s="53"/>
+      <c r="G103" s="53"/>
+      <c r="H103" s="53"/>
+      <c r="I103" s="53"/>
+      <c r="J103" s="53"/>
+      <c r="K103" s="54"/>
     </row>
     <row r="104" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B104" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="C104" s="51"/>
-      <c r="D104" s="51"/>
-      <c r="E104" s="51"/>
-      <c r="F104" s="51"/>
-      <c r="G104" s="51"/>
-      <c r="H104" s="51"/>
-      <c r="I104" s="51"/>
-      <c r="J104" s="51"/>
-      <c r="K104" s="52"/>
+      <c r="B104" s="52" t="s">
+        <v>249</v>
+      </c>
+      <c r="C104" s="53"/>
+      <c r="D104" s="53"/>
+      <c r="E104" s="53"/>
+      <c r="F104" s="53"/>
+      <c r="G104" s="53"/>
+      <c r="H104" s="53"/>
+      <c r="I104" s="53"/>
+      <c r="J104" s="53"/>
+      <c r="K104" s="54"/>
     </row>
     <row r="105" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="46">
@@ -6006,10 +6008,10 @@
         <v>59</v>
       </c>
       <c r="C105" s="43" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D105" s="44" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E105" s="44" t="s">
         <v>54</v>
@@ -6028,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="44" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="K105" s="47"/>
     </row>
@@ -6040,10 +6042,10 @@
         <v>59</v>
       </c>
       <c r="C106" s="43" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D106" s="44" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E106" s="44" t="s">
         <v>54</v>
@@ -6062,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="J106" s="44" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="K106" s="47"/>
     </row>
@@ -6074,16 +6076,16 @@
         <v>59</v>
       </c>
       <c r="C107" s="43" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D107" s="44" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="E107" s="44" t="s">
         <v>70</v>
       </c>
       <c r="F107" s="44" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G107" s="44">
         <v>2</v>
@@ -6096,7 +6098,7 @@
         <v>0.5</v>
       </c>
       <c r="J107" s="44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K107" s="47"/>
     </row>
@@ -6108,10 +6110,10 @@
         <v>59</v>
       </c>
       <c r="C108" s="43" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="D108" s="44" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E108" s="44" t="s">
         <v>60</v>
@@ -6130,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="J108" s="44" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K108" s="47"/>
     </row>
@@ -6142,10 +6144,10 @@
         <v>59</v>
       </c>
       <c r="C109" s="43" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D109" s="44" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E109" s="44" t="s">
         <v>60</v>
@@ -6164,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="J109" s="44" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K109" s="47"/>
     </row>
@@ -6176,10 +6178,10 @@
         <v>59</v>
       </c>
       <c r="C110" s="43" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D110" s="44" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E110" s="44" t="s">
         <v>57</v>
@@ -6198,7 +6200,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="44" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K110" s="47"/>
     </row>
@@ -6210,16 +6212,16 @@
         <v>59</v>
       </c>
       <c r="C111" s="43" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D111" s="44" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="E111" s="44" t="s">
         <v>70</v>
       </c>
       <c r="F111" s="44" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G111" s="44">
         <v>2</v>
@@ -6232,10 +6234,10 @@
         <v>0</v>
       </c>
       <c r="J111" s="44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K111" s="47" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -6246,16 +6248,16 @@
         <v>59</v>
       </c>
       <c r="C112" s="43" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D112" s="44" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E112" s="44" t="s">
         <v>70</v>
       </c>
       <c r="F112" s="44" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G112" s="44">
         <v>2</v>
@@ -6268,10 +6270,10 @@
         <v>0</v>
       </c>
       <c r="J112" s="44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K112" s="47" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -6299,53 +6301,53 @@
       <c r="K113" s="18"/>
     </row>
     <row r="114" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="70" t="s">
+      <c r="A114" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="B114" s="56"/>
-      <c r="C114" s="56"/>
-      <c r="D114" s="56"/>
-      <c r="E114" s="56"/>
-      <c r="F114" s="56"/>
-      <c r="G114" s="56"/>
-      <c r="H114" s="56"/>
-      <c r="I114" s="56"/>
-      <c r="J114" s="56"/>
-      <c r="K114" s="56"/>
+      <c r="B114" s="51"/>
+      <c r="C114" s="51"/>
+      <c r="D114" s="51"/>
+      <c r="E114" s="51"/>
+      <c r="F114" s="51"/>
+      <c r="G114" s="51"/>
+      <c r="H114" s="51"/>
+      <c r="I114" s="51"/>
+      <c r="J114" s="51"/>
+      <c r="K114" s="51"/>
     </row>
     <row r="115" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="B115" s="64" t="s">
-        <v>273</v>
-      </c>
-      <c r="C115" s="51"/>
-      <c r="D115" s="51"/>
-      <c r="E115" s="51"/>
-      <c r="F115" s="51"/>
-      <c r="G115" s="51"/>
-      <c r="H115" s="51"/>
-      <c r="I115" s="51"/>
-      <c r="J115" s="51"/>
-      <c r="K115" s="52"/>
+      <c r="B115" s="56" t="s">
+        <v>267</v>
+      </c>
+      <c r="C115" s="53"/>
+      <c r="D115" s="53"/>
+      <c r="E115" s="53"/>
+      <c r="F115" s="53"/>
+      <c r="G115" s="53"/>
+      <c r="H115" s="53"/>
+      <c r="I115" s="53"/>
+      <c r="J115" s="53"/>
+      <c r="K115" s="54"/>
     </row>
     <row r="116" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B116" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="C116" s="51"/>
-      <c r="D116" s="51"/>
-      <c r="E116" s="51"/>
-      <c r="F116" s="51"/>
-      <c r="G116" s="51"/>
-      <c r="H116" s="51"/>
-      <c r="I116" s="51"/>
-      <c r="J116" s="51"/>
-      <c r="K116" s="52"/>
+      <c r="B116" s="56" t="s">
+        <v>143</v>
+      </c>
+      <c r="C116" s="53"/>
+      <c r="D116" s="53"/>
+      <c r="E116" s="53"/>
+      <c r="F116" s="53"/>
+      <c r="G116" s="53"/>
+      <c r="H116" s="53"/>
+      <c r="I116" s="53"/>
+      <c r="J116" s="53"/>
+      <c r="K116" s="54"/>
     </row>
     <row r="117" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="46">
@@ -6355,10 +6357,10 @@
         <v>59</v>
       </c>
       <c r="C117" s="43" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D117" s="44" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E117" s="44" t="s">
         <v>57</v>
@@ -6377,7 +6379,7 @@
         <v>0</v>
       </c>
       <c r="J117" s="44" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="K117" s="47"/>
     </row>
@@ -6389,10 +6391,10 @@
         <v>59</v>
       </c>
       <c r="C118" s="43" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="D118" s="44" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="E118" s="44" t="s">
         <v>60</v>
@@ -6411,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="44" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K118" s="47"/>
     </row>
@@ -6423,10 +6425,10 @@
         <v>59</v>
       </c>
       <c r="C119" s="43" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D119" s="44" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="E119" s="44" t="s">
         <v>57</v>
@@ -6445,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="J119" s="44" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K119" s="47"/>
     </row>
@@ -6457,10 +6459,10 @@
         <v>59</v>
       </c>
       <c r="C120" s="43" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D120" s="44" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="E120" s="44" t="s">
         <v>57</v>
@@ -6479,7 +6481,7 @@
         <v>0</v>
       </c>
       <c r="J120" s="44" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K120" s="47"/>
     </row>
@@ -6491,10 +6493,10 @@
         <v>59</v>
       </c>
       <c r="C121" s="48" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D121" s="44" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="E121" s="39" t="s">
         <v>66</v>
@@ -6523,10 +6525,10 @@
         <v>59</v>
       </c>
       <c r="C122" s="43" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D122" s="44" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="E122" s="44" t="s">
         <v>57</v>
@@ -6545,7 +6547,7 @@
         <v>0</v>
       </c>
       <c r="J122" s="44" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K122" s="47"/>
     </row>
@@ -6557,10 +6559,10 @@
         <v>59</v>
       </c>
       <c r="C123" s="43" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="D123" s="44" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E123" s="44" t="s">
         <v>57</v>
@@ -6579,7 +6581,7 @@
         <v>0</v>
       </c>
       <c r="J123" s="44" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="K123" s="47"/>
     </row>
@@ -6591,10 +6593,10 @@
         <v>59</v>
       </c>
       <c r="C124" s="43" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="D124" s="44" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E124" s="44" t="s">
         <v>48</v>
@@ -6613,7 +6615,7 @@
         <v>0</v>
       </c>
       <c r="J124" s="44" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="K124" s="47"/>
     </row>
@@ -6625,10 +6627,10 @@
         <v>59</v>
       </c>
       <c r="C125" s="43" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="D125" s="44" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E125" s="44" t="s">
         <v>68</v>
@@ -6647,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="44" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="K125" s="47"/>
     </row>
@@ -6676,53 +6678,53 @@
       <c r="K126" s="18"/>
     </row>
     <row r="127" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="65" t="s">
+      <c r="A127" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="B127" s="51"/>
-      <c r="C127" s="51"/>
-      <c r="D127" s="51"/>
-      <c r="E127" s="51"/>
-      <c r="F127" s="51"/>
-      <c r="G127" s="51"/>
-      <c r="H127" s="51"/>
-      <c r="I127" s="51"/>
-      <c r="J127" s="51"/>
-      <c r="K127" s="52"/>
+      <c r="B127" s="53"/>
+      <c r="C127" s="53"/>
+      <c r="D127" s="53"/>
+      <c r="E127" s="53"/>
+      <c r="F127" s="53"/>
+      <c r="G127" s="53"/>
+      <c r="H127" s="53"/>
+      <c r="I127" s="53"/>
+      <c r="J127" s="53"/>
+      <c r="K127" s="54"/>
     </row>
     <row r="128" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B128" s="66" t="s">
-        <v>293</v>
-      </c>
-      <c r="C128" s="51"/>
-      <c r="D128" s="51"/>
-      <c r="E128" s="51"/>
-      <c r="F128" s="51"/>
-      <c r="G128" s="51"/>
-      <c r="H128" s="51"/>
-      <c r="I128" s="51"/>
-      <c r="J128" s="51"/>
-      <c r="K128" s="52"/>
+      <c r="B128" s="58" t="s">
+        <v>287</v>
+      </c>
+      <c r="C128" s="53"/>
+      <c r="D128" s="53"/>
+      <c r="E128" s="53"/>
+      <c r="F128" s="53"/>
+      <c r="G128" s="53"/>
+      <c r="H128" s="53"/>
+      <c r="I128" s="53"/>
+      <c r="J128" s="53"/>
+      <c r="K128" s="54"/>
     </row>
     <row r="129" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B129" s="66" t="s">
-        <v>294</v>
-      </c>
-      <c r="C129" s="51"/>
-      <c r="D129" s="51"/>
-      <c r="E129" s="51"/>
-      <c r="F129" s="51"/>
-      <c r="G129" s="51"/>
-      <c r="H129" s="51"/>
-      <c r="I129" s="51"/>
-      <c r="J129" s="51"/>
-      <c r="K129" s="52"/>
+      <c r="B129" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="C129" s="53"/>
+      <c r="D129" s="53"/>
+      <c r="E129" s="53"/>
+      <c r="F129" s="53"/>
+      <c r="G129" s="53"/>
+      <c r="H129" s="53"/>
+      <c r="I129" s="53"/>
+      <c r="J129" s="53"/>
+      <c r="K129" s="54"/>
     </row>
     <row r="130" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="46">
@@ -6732,10 +6734,10 @@
         <v>59</v>
       </c>
       <c r="C130" s="43" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D130" s="44" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="E130" s="44" t="s">
         <v>66</v>
@@ -6754,7 +6756,7 @@
         <v>0</v>
       </c>
       <c r="J130" s="44" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="K130" s="47"/>
     </row>
@@ -6766,10 +6768,10 @@
         <v>59</v>
       </c>
       <c r="C131" s="43" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D131" s="44" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E131" s="44" t="s">
         <v>54</v>
@@ -6798,10 +6800,10 @@
         <v>59</v>
       </c>
       <c r="C132" s="43" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D132" s="44" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E132" s="44" t="s">
         <v>57</v>
@@ -6820,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="44" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="K132" s="47"/>
     </row>
@@ -6832,10 +6834,10 @@
         <v>59</v>
       </c>
       <c r="C133" s="43" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="D133" s="44" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E133" s="44" t="s">
         <v>57</v>
@@ -6854,7 +6856,7 @@
         <v>0</v>
       </c>
       <c r="J133" s="44" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="K133" s="47"/>
     </row>
@@ -6866,10 +6868,10 @@
         <v>59</v>
       </c>
       <c r="C134" s="43" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D134" s="44" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="E134" s="44" t="s">
         <v>54</v>
@@ -6888,7 +6890,7 @@
         <v>0</v>
       </c>
       <c r="J134" s="44" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="K134" s="47"/>
     </row>
@@ -6900,10 +6902,10 @@
         <v>59</v>
       </c>
       <c r="C135" s="43" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="D135" s="44" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="E135" s="44" t="s">
         <v>54</v>
@@ -6922,7 +6924,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="44" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="K135" s="47"/>
     </row>
@@ -6934,10 +6936,10 @@
         <v>59</v>
       </c>
       <c r="C136" s="43" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="D136" s="44" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="E136" s="44" t="s">
         <v>54</v>
@@ -6956,7 +6958,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="44" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="K136" s="47"/>
     </row>
@@ -6985,53 +6987,53 @@
       <c r="K137" s="18"/>
     </row>
     <row r="138" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="67" t="s">
+      <c r="A138" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B138" s="51"/>
-      <c r="C138" s="51"/>
-      <c r="D138" s="51"/>
-      <c r="E138" s="51"/>
-      <c r="F138" s="51"/>
-      <c r="G138" s="51"/>
-      <c r="H138" s="51"/>
-      <c r="I138" s="51"/>
-      <c r="J138" s="51"/>
-      <c r="K138" s="52"/>
+      <c r="B138" s="53"/>
+      <c r="C138" s="53"/>
+      <c r="D138" s="53"/>
+      <c r="E138" s="53"/>
+      <c r="F138" s="53"/>
+      <c r="G138" s="53"/>
+      <c r="H138" s="53"/>
+      <c r="I138" s="53"/>
+      <c r="J138" s="53"/>
+      <c r="K138" s="54"/>
     </row>
     <row r="139" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B139" s="61" t="s">
-        <v>312</v>
-      </c>
-      <c r="C139" s="51"/>
-      <c r="D139" s="51"/>
-      <c r="E139" s="51"/>
-      <c r="F139" s="51"/>
-      <c r="G139" s="51"/>
-      <c r="H139" s="51"/>
-      <c r="I139" s="51"/>
-      <c r="J139" s="51"/>
-      <c r="K139" s="52"/>
+      <c r="B139" s="60" t="s">
+        <v>306</v>
+      </c>
+      <c r="C139" s="53"/>
+      <c r="D139" s="53"/>
+      <c r="E139" s="53"/>
+      <c r="F139" s="53"/>
+      <c r="G139" s="53"/>
+      <c r="H139" s="53"/>
+      <c r="I139" s="53"/>
+      <c r="J139" s="53"/>
+      <c r="K139" s="54"/>
     </row>
     <row r="140" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B140" s="61" t="s">
-        <v>313</v>
-      </c>
-      <c r="C140" s="51"/>
-      <c r="D140" s="51"/>
-      <c r="E140" s="51"/>
-      <c r="F140" s="51"/>
-      <c r="G140" s="51"/>
-      <c r="H140" s="51"/>
-      <c r="I140" s="51"/>
-      <c r="J140" s="51"/>
-      <c r="K140" s="52"/>
+      <c r="B140" s="60" t="s">
+        <v>307</v>
+      </c>
+      <c r="C140" s="53"/>
+      <c r="D140" s="53"/>
+      <c r="E140" s="53"/>
+      <c r="F140" s="53"/>
+      <c r="G140" s="53"/>
+      <c r="H140" s="53"/>
+      <c r="I140" s="53"/>
+      <c r="J140" s="53"/>
+      <c r="K140" s="54"/>
     </row>
     <row r="141" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="46">
@@ -7041,10 +7043,10 @@
         <v>59</v>
       </c>
       <c r="C141" s="43" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D141" s="44" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="E141" s="44" t="s">
         <v>60</v>
@@ -7063,7 +7065,7 @@
         <v>0</v>
       </c>
       <c r="J141" s="44" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="K141" s="47"/>
     </row>
@@ -7075,10 +7077,10 @@
         <v>59</v>
       </c>
       <c r="C142" s="43" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="D142" s="44" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="E142" s="44" t="s">
         <v>57</v>
@@ -7097,7 +7099,7 @@
         <v>0</v>
       </c>
       <c r="J142" s="44" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="K142" s="47"/>
     </row>
@@ -7109,10 +7111,10 @@
         <v>59</v>
       </c>
       <c r="C143" s="43" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D143" s="44" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E143" s="44" t="s">
         <v>54</v>
@@ -7131,7 +7133,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="44" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="K143" s="47"/>
     </row>
@@ -7143,10 +7145,10 @@
         <v>59</v>
       </c>
       <c r="C144" s="43" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D144" s="44" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E144" s="44" t="s">
         <v>60</v>
@@ -7165,10 +7167,10 @@
         <v>0</v>
       </c>
       <c r="J144" s="44" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K144" s="47" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="145" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -7179,10 +7181,10 @@
         <v>59</v>
       </c>
       <c r="C145" s="48" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D145" s="39" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="E145" s="39" t="s">
         <v>66</v>
@@ -7211,10 +7213,10 @@
         <v>59</v>
       </c>
       <c r="C146" s="43" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="D146" s="44" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="E146" s="44" t="s">
         <v>48</v>
@@ -7233,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="J146" s="44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K146" s="47"/>
     </row>
@@ -7245,10 +7247,10 @@
         <v>59</v>
       </c>
       <c r="C147" s="43" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D147" s="44" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E147" s="44" t="s">
         <v>54</v>
@@ -7267,7 +7269,7 @@
         <v>0</v>
       </c>
       <c r="J147" s="44" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="K147" s="47"/>
     </row>
@@ -7279,10 +7281,10 @@
         <v>59</v>
       </c>
       <c r="C148" s="43" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D148" s="44" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="E148" s="44" t="s">
         <v>54</v>
@@ -7301,7 +7303,7 @@
         <v>0</v>
       </c>
       <c r="J148" s="44" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="K148" s="47"/>
     </row>
@@ -7313,10 +7315,10 @@
         <v>59</v>
       </c>
       <c r="C149" s="43" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D149" s="44" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="E149" s="44" t="s">
         <v>60</v>
@@ -7335,7 +7337,7 @@
         <v>0</v>
       </c>
       <c r="J149" s="44" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="K149" s="47"/>
     </row>
@@ -7364,53 +7366,53 @@
       <c r="K150" s="18"/>
     </row>
     <row r="151" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="62" t="s">
+      <c r="A151" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="B151" s="51"/>
-      <c r="C151" s="51"/>
-      <c r="D151" s="51"/>
-      <c r="E151" s="51"/>
-      <c r="F151" s="51"/>
-      <c r="G151" s="51"/>
-      <c r="H151" s="51"/>
-      <c r="I151" s="51"/>
-      <c r="J151" s="51"/>
-      <c r="K151" s="52"/>
+      <c r="B151" s="53"/>
+      <c r="C151" s="53"/>
+      <c r="D151" s="53"/>
+      <c r="E151" s="53"/>
+      <c r="F151" s="53"/>
+      <c r="G151" s="53"/>
+      <c r="H151" s="53"/>
+      <c r="I151" s="53"/>
+      <c r="J151" s="53"/>
+      <c r="K151" s="54"/>
     </row>
     <row r="152" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B152" s="63" t="s">
-        <v>335</v>
-      </c>
-      <c r="C152" s="51"/>
-      <c r="D152" s="51"/>
-      <c r="E152" s="51"/>
-      <c r="F152" s="51"/>
-      <c r="G152" s="51"/>
-      <c r="H152" s="51"/>
-      <c r="I152" s="51"/>
-      <c r="J152" s="51"/>
-      <c r="K152" s="52"/>
+      <c r="B152" s="62" t="s">
+        <v>329</v>
+      </c>
+      <c r="C152" s="53"/>
+      <c r="D152" s="53"/>
+      <c r="E152" s="53"/>
+      <c r="F152" s="53"/>
+      <c r="G152" s="53"/>
+      <c r="H152" s="53"/>
+      <c r="I152" s="53"/>
+      <c r="J152" s="53"/>
+      <c r="K152" s="54"/>
     </row>
     <row r="153" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="B153" s="63" t="s">
-        <v>149</v>
-      </c>
-      <c r="C153" s="51"/>
-      <c r="D153" s="51"/>
-      <c r="E153" s="51"/>
-      <c r="F153" s="51"/>
-      <c r="G153" s="51"/>
-      <c r="H153" s="51"/>
-      <c r="I153" s="51"/>
-      <c r="J153" s="51"/>
-      <c r="K153" s="52"/>
+      <c r="B153" s="62" t="s">
+        <v>143</v>
+      </c>
+      <c r="C153" s="53"/>
+      <c r="D153" s="53"/>
+      <c r="E153" s="53"/>
+      <c r="F153" s="53"/>
+      <c r="G153" s="53"/>
+      <c r="H153" s="53"/>
+      <c r="I153" s="53"/>
+      <c r="J153" s="53"/>
+      <c r="K153" s="54"/>
     </row>
     <row r="154" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="46">
@@ -7420,10 +7422,10 @@
         <v>59</v>
       </c>
       <c r="C154" s="43" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D154" s="44" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="E154" s="44" t="s">
         <v>54</v>
@@ -7442,7 +7444,7 @@
         <v>0</v>
       </c>
       <c r="J154" s="44" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="K154" s="24"/>
     </row>
@@ -7454,10 +7456,10 @@
         <v>59</v>
       </c>
       <c r="C155" s="43" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="D155" s="44" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E155" s="44" t="s">
         <v>54</v>
@@ -7476,7 +7478,7 @@
         <v>0</v>
       </c>
       <c r="J155" s="44" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="K155" s="24"/>
     </row>
@@ -7488,10 +7490,10 @@
         <v>59</v>
       </c>
       <c r="C156" s="43" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D156" s="44" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E156" s="44" t="s">
         <v>54</v>
@@ -7510,7 +7512,7 @@
         <v>0</v>
       </c>
       <c r="J156" s="44" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="K156" s="24"/>
     </row>
@@ -7522,10 +7524,10 @@
         <v>59</v>
       </c>
       <c r="C157" s="43" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D157" s="44" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="E157" s="44" t="s">
         <v>54</v>
@@ -7544,7 +7546,7 @@
         <v>0</v>
       </c>
       <c r="J157" s="44" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="K157" s="24"/>
     </row>
@@ -7556,10 +7558,10 @@
         <v>59</v>
       </c>
       <c r="C158" s="43" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D158" s="44" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="E158" s="44" t="s">
         <v>60</v>
@@ -7588,10 +7590,10 @@
         <v>59</v>
       </c>
       <c r="C159" s="43" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D159" s="44" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E159" s="44" t="s">
         <v>70</v>
@@ -7620,10 +7622,10 @@
         <v>59</v>
       </c>
       <c r="C160" s="43" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D160" s="44" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="E160" s="44" t="s">
         <v>54</v>
@@ -7642,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="J160" s="44" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="K160" s="24"/>
     </row>
@@ -7671,53 +7673,53 @@
       <c r="K161" s="18"/>
     </row>
     <row r="162" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="60" t="s">
+      <c r="A162" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="B162" s="51"/>
-      <c r="C162" s="51"/>
-      <c r="D162" s="51"/>
-      <c r="E162" s="51"/>
-      <c r="F162" s="51"/>
-      <c r="G162" s="51"/>
-      <c r="H162" s="51"/>
-      <c r="I162" s="51"/>
-      <c r="J162" s="51"/>
-      <c r="K162" s="52"/>
+      <c r="B162" s="53"/>
+      <c r="C162" s="53"/>
+      <c r="D162" s="53"/>
+      <c r="E162" s="53"/>
+      <c r="F162" s="53"/>
+      <c r="G162" s="53"/>
+      <c r="H162" s="53"/>
+      <c r="I162" s="53"/>
+      <c r="J162" s="53"/>
+      <c r="K162" s="54"/>
     </row>
     <row r="163" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B163" s="53" t="s">
-        <v>350</v>
-      </c>
-      <c r="C163" s="51"/>
-      <c r="D163" s="51"/>
-      <c r="E163" s="51"/>
-      <c r="F163" s="51"/>
-      <c r="G163" s="51"/>
-      <c r="H163" s="51"/>
-      <c r="I163" s="51"/>
-      <c r="J163" s="51"/>
-      <c r="K163" s="52"/>
+      <c r="B163" s="73" t="s">
+        <v>344</v>
+      </c>
+      <c r="C163" s="53"/>
+      <c r="D163" s="53"/>
+      <c r="E163" s="53"/>
+      <c r="F163" s="53"/>
+      <c r="G163" s="53"/>
+      <c r="H163" s="53"/>
+      <c r="I163" s="53"/>
+      <c r="J163" s="53"/>
+      <c r="K163" s="54"/>
     </row>
     <row r="164" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B164" s="53" t="s">
-        <v>351</v>
-      </c>
-      <c r="C164" s="51"/>
-      <c r="D164" s="51"/>
-      <c r="E164" s="51"/>
-      <c r="F164" s="51"/>
-      <c r="G164" s="51"/>
-      <c r="H164" s="51"/>
-      <c r="I164" s="51"/>
-      <c r="J164" s="51"/>
-      <c r="K164" s="52"/>
+      <c r="B164" s="73" t="s">
+        <v>345</v>
+      </c>
+      <c r="C164" s="53"/>
+      <c r="D164" s="53"/>
+      <c r="E164" s="53"/>
+      <c r="F164" s="53"/>
+      <c r="G164" s="53"/>
+      <c r="H164" s="53"/>
+      <c r="I164" s="53"/>
+      <c r="J164" s="53"/>
+      <c r="K164" s="54"/>
     </row>
     <row r="165" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="46">
@@ -7727,10 +7729,10 @@
         <v>59</v>
       </c>
       <c r="C165" s="43" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D165" s="44" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E165" s="44" t="s">
         <v>66</v>
@@ -7749,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="J165" s="44" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="K165" s="47"/>
     </row>
@@ -7761,10 +7763,10 @@
         <v>59</v>
       </c>
       <c r="C166" s="43" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D166" s="44" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="E166" s="44" t="s">
         <v>57</v>
@@ -7783,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="J166" s="44" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="K166" s="47"/>
     </row>
@@ -7795,10 +7797,10 @@
         <v>59</v>
       </c>
       <c r="C167" s="43" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D167" s="44" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="E167" s="44" t="s">
         <v>60</v>
@@ -7817,7 +7819,7 @@
         <v>0</v>
       </c>
       <c r="J167" s="44" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="K167" s="47"/>
     </row>
@@ -7829,16 +7831,16 @@
         <v>59</v>
       </c>
       <c r="C168" s="43" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="D168" s="44" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="E168" s="44" t="s">
         <v>57</v>
       </c>
       <c r="F168" s="44" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G168" s="44">
         <v>1.5</v>
@@ -7851,10 +7853,10 @@
         <v>0</v>
       </c>
       <c r="J168" s="44" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="K168" s="47" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="169" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -7865,10 +7867,10 @@
         <v>59</v>
       </c>
       <c r="C169" s="43" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D169" s="44" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E169" s="44" t="s">
         <v>57</v>
@@ -7887,7 +7889,7 @@
         <v>0</v>
       </c>
       <c r="J169" s="44" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="K169" s="47"/>
     </row>
@@ -7899,10 +7901,10 @@
         <v>59</v>
       </c>
       <c r="C170" s="43" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D170" s="44" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E170" s="44" t="s">
         <v>57</v>
@@ -7921,7 +7923,7 @@
         <v>0</v>
       </c>
       <c r="J170" s="44" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="K170" s="47"/>
     </row>
@@ -7933,10 +7935,10 @@
         <v>59</v>
       </c>
       <c r="C171" s="43" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="D171" s="44" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E171" s="44" t="s">
         <v>54</v>
@@ -7955,7 +7957,7 @@
         <v>0</v>
       </c>
       <c r="J171" s="44" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="K171" s="47"/>
     </row>
@@ -7967,10 +7969,10 @@
         <v>59</v>
       </c>
       <c r="C172" s="43" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D172" s="44" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="E172" s="44" t="s">
         <v>57</v>
@@ -8016,53 +8018,53 @@
       <c r="K173" s="18"/>
     </row>
     <row r="174" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="59" t="s">
+      <c r="A174" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="B174" s="51"/>
-      <c r="C174" s="51"/>
-      <c r="D174" s="51"/>
-      <c r="E174" s="51"/>
-      <c r="F174" s="51"/>
-      <c r="G174" s="51"/>
-      <c r="H174" s="51"/>
-      <c r="I174" s="51"/>
-      <c r="J174" s="51"/>
-      <c r="K174" s="52"/>
+      <c r="B174" s="53"/>
+      <c r="C174" s="53"/>
+      <c r="D174" s="53"/>
+      <c r="E174" s="53"/>
+      <c r="F174" s="53"/>
+      <c r="G174" s="53"/>
+      <c r="H174" s="53"/>
+      <c r="I174" s="53"/>
+      <c r="J174" s="53"/>
+      <c r="K174" s="54"/>
     </row>
     <row r="175" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B175" s="50" t="s">
-        <v>370</v>
-      </c>
-      <c r="C175" s="51"/>
-      <c r="D175" s="51"/>
-      <c r="E175" s="51"/>
-      <c r="F175" s="51"/>
-      <c r="G175" s="51"/>
-      <c r="H175" s="51"/>
-      <c r="I175" s="51"/>
-      <c r="J175" s="51"/>
-      <c r="K175" s="52"/>
+      <c r="B175" s="75" t="s">
+        <v>364</v>
+      </c>
+      <c r="C175" s="53"/>
+      <c r="D175" s="53"/>
+      <c r="E175" s="53"/>
+      <c r="F175" s="53"/>
+      <c r="G175" s="53"/>
+      <c r="H175" s="53"/>
+      <c r="I175" s="53"/>
+      <c r="J175" s="53"/>
+      <c r="K175" s="54"/>
     </row>
     <row r="176" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B176" s="50" t="s">
-        <v>371</v>
-      </c>
-      <c r="C176" s="51"/>
-      <c r="D176" s="51"/>
-      <c r="E176" s="51"/>
-      <c r="F176" s="51"/>
-      <c r="G176" s="51"/>
-      <c r="H176" s="51"/>
-      <c r="I176" s="51"/>
-      <c r="J176" s="51"/>
-      <c r="K176" s="52"/>
+      <c r="B176" s="75" t="s">
+        <v>365</v>
+      </c>
+      <c r="C176" s="53"/>
+      <c r="D176" s="53"/>
+      <c r="E176" s="53"/>
+      <c r="F176" s="53"/>
+      <c r="G176" s="53"/>
+      <c r="H176" s="53"/>
+      <c r="I176" s="53"/>
+      <c r="J176" s="53"/>
+      <c r="K176" s="54"/>
     </row>
     <row r="177" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="46">
@@ -8072,10 +8074,10 @@
         <v>59</v>
       </c>
       <c r="C177" s="43" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D177" s="44" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="E177" s="44" t="s">
         <v>60</v>
@@ -8094,7 +8096,7 @@
         <v>0</v>
       </c>
       <c r="J177" s="44" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="K177" s="47"/>
     </row>
@@ -8106,10 +8108,10 @@
         <v>59</v>
       </c>
       <c r="C178" s="43" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="D178" s="44" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="E178" s="44" t="s">
         <v>57</v>
@@ -8128,7 +8130,7 @@
         <v>0</v>
       </c>
       <c r="J178" s="44" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K178" s="47"/>
     </row>
@@ -8140,10 +8142,10 @@
         <v>59</v>
       </c>
       <c r="C179" s="43" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="D179" s="44" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E179" s="44" t="s">
         <v>57</v>
@@ -8162,7 +8164,7 @@
         <v>0</v>
       </c>
       <c r="J179" s="44" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="K179" s="47"/>
     </row>
@@ -8174,10 +8176,10 @@
         <v>59</v>
       </c>
       <c r="C180" s="43" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="D180" s="44" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="E180" s="44" t="s">
         <v>57</v>
@@ -8206,10 +8208,10 @@
         <v>59</v>
       </c>
       <c r="C181" s="43" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="D181" s="44" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="E181" s="44" t="s">
         <v>57</v>
@@ -8228,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="J181" s="44" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="K181" s="47"/>
     </row>
@@ -8240,10 +8242,10 @@
         <v>59</v>
       </c>
       <c r="C182" s="43" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="D182" s="44" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="E182" s="44" t="s">
         <v>60</v>
@@ -8262,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="J182" s="44" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="K182" s="47"/>
     </row>
@@ -8274,10 +8276,10 @@
         <v>59</v>
       </c>
       <c r="C183" s="43" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="D183" s="44" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E183" s="44" t="s">
         <v>70</v>
@@ -8296,7 +8298,7 @@
         <v>0</v>
       </c>
       <c r="J183" s="44" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="K183" s="47"/>
     </row>
@@ -8308,10 +8310,10 @@
         <v>59</v>
       </c>
       <c r="C184" s="48" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D184" s="39" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="E184" s="39" t="s">
         <v>66</v>
@@ -8340,10 +8342,10 @@
         <v>59</v>
       </c>
       <c r="C185" s="43" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D185" s="44" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="E185" s="44" t="s">
         <v>68</v>
@@ -8362,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="J185" s="44" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="K185" s="47"/>
     </row>
@@ -8391,53 +8393,53 @@
       <c r="K186" s="18"/>
     </row>
     <row r="187" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A187" s="54" t="s">
+      <c r="A187" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="B187" s="51"/>
-      <c r="C187" s="51"/>
-      <c r="D187" s="51"/>
-      <c r="E187" s="51"/>
-      <c r="F187" s="51"/>
-      <c r="G187" s="51"/>
-      <c r="H187" s="51"/>
-      <c r="I187" s="51"/>
-      <c r="J187" s="51"/>
-      <c r="K187" s="52"/>
+      <c r="B187" s="53"/>
+      <c r="C187" s="53"/>
+      <c r="D187" s="53"/>
+      <c r="E187" s="53"/>
+      <c r="F187" s="53"/>
+      <c r="G187" s="53"/>
+      <c r="H187" s="53"/>
+      <c r="I187" s="53"/>
+      <c r="J187" s="53"/>
+      <c r="K187" s="54"/>
     </row>
     <row r="188" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B188" s="55" t="s">
-        <v>393</v>
-      </c>
-      <c r="C188" s="56"/>
-      <c r="D188" s="56"/>
-      <c r="E188" s="56"/>
-      <c r="F188" s="56"/>
-      <c r="G188" s="56"/>
-      <c r="H188" s="56"/>
-      <c r="I188" s="56"/>
-      <c r="J188" s="56"/>
-      <c r="K188" s="57"/>
+      <c r="B188" s="76" t="s">
+        <v>387</v>
+      </c>
+      <c r="C188" s="51"/>
+      <c r="D188" s="51"/>
+      <c r="E188" s="51"/>
+      <c r="F188" s="51"/>
+      <c r="G188" s="51"/>
+      <c r="H188" s="51"/>
+      <c r="I188" s="51"/>
+      <c r="J188" s="51"/>
+      <c r="K188" s="77"/>
     </row>
     <row r="189" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="B189" s="58" t="s">
-        <v>394</v>
-      </c>
-      <c r="C189" s="56"/>
-      <c r="D189" s="56"/>
-      <c r="E189" s="56"/>
-      <c r="F189" s="56"/>
-      <c r="G189" s="56"/>
-      <c r="H189" s="56"/>
-      <c r="I189" s="56"/>
-      <c r="J189" s="56"/>
-      <c r="K189" s="57"/>
+      <c r="B189" s="78" t="s">
+        <v>388</v>
+      </c>
+      <c r="C189" s="51"/>
+      <c r="D189" s="51"/>
+      <c r="E189" s="51"/>
+      <c r="F189" s="51"/>
+      <c r="G189" s="51"/>
+      <c r="H189" s="51"/>
+      <c r="I189" s="51"/>
+      <c r="J189" s="51"/>
+      <c r="K189" s="77"/>
     </row>
     <row r="190" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="46">
@@ -8447,10 +8449,10 @@
         <v>59</v>
       </c>
       <c r="C190" s="43" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="D190" s="44" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="E190" s="44" t="s">
         <v>48</v>
@@ -8479,10 +8481,10 @@
         <v>59</v>
       </c>
       <c r="C191" s="43" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D191" s="44" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="E191" s="44" t="s">
         <v>51</v>
@@ -8502,7 +8504,7 @@
       </c>
       <c r="J191" s="39"/>
       <c r="K191" s="39" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
     </row>
     <row r="192" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -8513,10 +8515,10 @@
         <v>59</v>
       </c>
       <c r="C192" s="43" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="D192" s="44" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="E192" s="44" t="s">
         <v>51</v>
@@ -8545,10 +8547,10 @@
         <v>59</v>
       </c>
       <c r="C193" s="43" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D193" s="44" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="E193" s="44" t="s">
         <v>51</v>
@@ -8577,10 +8579,10 @@
         <v>59</v>
       </c>
       <c r="C194" s="43" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="D194" s="44" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="E194" s="44" t="s">
         <v>57</v>
@@ -8599,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="J194" s="44" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K194" s="47"/>
     </row>
@@ -8611,16 +8613,16 @@
         <v>59</v>
       </c>
       <c r="C195" s="43" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="D195" s="44" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="E195" s="44" t="s">
         <v>57</v>
       </c>
       <c r="F195" s="44" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G195" s="44">
         <v>1.5</v>
@@ -8634,7 +8636,7 @@
       </c>
       <c r="J195" s="44"/>
       <c r="K195" s="47" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="196" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -8645,10 +8647,10 @@
         <v>59</v>
       </c>
       <c r="C196" s="48" t="s">
+        <v>499</v>
+      </c>
+      <c r="D196" s="44" t="s">
         <v>505</v>
-      </c>
-      <c r="D196" s="44" t="s">
-        <v>511</v>
       </c>
       <c r="E196" s="39" t="s">
         <v>66</v>
@@ -8668,7 +8670,7 @@
       </c>
       <c r="J196" s="44"/>
       <c r="K196" s="47" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
     </row>
     <row r="197" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -8679,10 +8681,10 @@
         <v>59</v>
       </c>
       <c r="C197" s="43" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="D197" s="44" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="E197" s="44" t="s">
         <v>54</v>
@@ -8701,7 +8703,7 @@
         <v>0</v>
       </c>
       <c r="J197" s="44" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="K197" s="47"/>
     </row>
@@ -8713,10 +8715,10 @@
         <v>59</v>
       </c>
       <c r="C198" s="43" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D198" s="44" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="E198" s="44" t="s">
         <v>57</v>
@@ -8735,7 +8737,7 @@
         <v>0</v>
       </c>
       <c r="J198" s="44" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="K198" s="47"/>
     </row>
@@ -8764,53 +8766,53 @@
       <c r="K199" s="18"/>
     </row>
     <row r="200" spans="1:11" s="42" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="59" t="s">
-        <v>411</v>
-      </c>
-      <c r="B200" s="51"/>
-      <c r="C200" s="51"/>
-      <c r="D200" s="51"/>
-      <c r="E200" s="51"/>
-      <c r="F200" s="51"/>
-      <c r="G200" s="51"/>
-      <c r="H200" s="51"/>
-      <c r="I200" s="51"/>
-      <c r="J200" s="51"/>
-      <c r="K200" s="52"/>
+      <c r="A200" s="74" t="s">
+        <v>405</v>
+      </c>
+      <c r="B200" s="53"/>
+      <c r="C200" s="53"/>
+      <c r="D200" s="53"/>
+      <c r="E200" s="53"/>
+      <c r="F200" s="53"/>
+      <c r="G200" s="53"/>
+      <c r="H200" s="53"/>
+      <c r="I200" s="53"/>
+      <c r="J200" s="53"/>
+      <c r="K200" s="54"/>
     </row>
     <row r="201" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A201" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B201" s="50" t="s">
-        <v>415</v>
-      </c>
-      <c r="C201" s="51"/>
-      <c r="D201" s="51"/>
-      <c r="E201" s="51"/>
-      <c r="F201" s="51"/>
-      <c r="G201" s="51"/>
-      <c r="H201" s="51"/>
-      <c r="I201" s="51"/>
-      <c r="J201" s="51"/>
-      <c r="K201" s="52"/>
+      <c r="B201" s="75" t="s">
+        <v>409</v>
+      </c>
+      <c r="C201" s="53"/>
+      <c r="D201" s="53"/>
+      <c r="E201" s="53"/>
+      <c r="F201" s="53"/>
+      <c r="G201" s="53"/>
+      <c r="H201" s="53"/>
+      <c r="I201" s="53"/>
+      <c r="J201" s="53"/>
+      <c r="K201" s="54"/>
     </row>
     <row r="202" spans="1:11" s="42" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B202" s="50" t="s">
-        <v>416</v>
-      </c>
-      <c r="C202" s="51"/>
-      <c r="D202" s="51"/>
-      <c r="E202" s="51"/>
-      <c r="F202" s="51"/>
-      <c r="G202" s="51"/>
-      <c r="H202" s="51"/>
-      <c r="I202" s="51"/>
-      <c r="J202" s="51"/>
-      <c r="K202" s="52"/>
+      <c r="B202" s="75" t="s">
+        <v>410</v>
+      </c>
+      <c r="C202" s="53"/>
+      <c r="D202" s="53"/>
+      <c r="E202" s="53"/>
+      <c r="F202" s="53"/>
+      <c r="G202" s="53"/>
+      <c r="H202" s="53"/>
+      <c r="I202" s="53"/>
+      <c r="J202" s="53"/>
+      <c r="K202" s="54"/>
     </row>
     <row r="203" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A203" s="46">
@@ -8820,10 +8822,10 @@
         <v>59</v>
       </c>
       <c r="C203" s="43" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D203" s="44" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="E203" s="44" t="s">
         <v>51</v>
@@ -8843,7 +8845,7 @@
       </c>
       <c r="J203" s="44"/>
       <c r="K203" s="39" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
     </row>
     <row r="204" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -8854,10 +8856,10 @@
         <v>59</v>
       </c>
       <c r="C204" s="43" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D204" s="44" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="E204" s="44" t="s">
         <v>51</v>
@@ -8886,10 +8888,10 @@
         <v>59</v>
       </c>
       <c r="C205" s="43" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D205" s="44" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="E205" s="44" t="s">
         <v>51</v>
@@ -8918,10 +8920,10 @@
         <v>59</v>
       </c>
       <c r="C206" s="43" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D206" s="44" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="E206" s="44" t="s">
         <v>57</v>
@@ -8940,7 +8942,7 @@
         <v>0</v>
       </c>
       <c r="J206" s="44" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="K206" s="47"/>
     </row>
@@ -8952,10 +8954,10 @@
         <v>59</v>
       </c>
       <c r="C207" s="43" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D207" s="44" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E207" s="44" t="s">
         <v>57</v>
@@ -8974,7 +8976,7 @@
         <v>0</v>
       </c>
       <c r="J207" s="44" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="K207" s="47"/>
     </row>
@@ -8986,10 +8988,10 @@
         <v>59</v>
       </c>
       <c r="C208" s="43" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="D208" s="44" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E208" s="44" t="s">
         <v>60</v>
@@ -9018,10 +9020,10 @@
         <v>59</v>
       </c>
       <c r="C209" s="43" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="D209" s="44" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="E209" s="44" t="s">
         <v>54</v>
@@ -9040,7 +9042,7 @@
         <v>0</v>
       </c>
       <c r="J209" s="44" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="K209" s="47"/>
     </row>
@@ -9052,10 +9054,10 @@
         <v>59</v>
       </c>
       <c r="C210" s="43" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="D210" s="44" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E210" s="44" t="s">
         <v>54</v>
@@ -9074,7 +9076,7 @@
         <v>0</v>
       </c>
       <c r="J210" s="44" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="K210" s="47"/>
     </row>
@@ -9103,53 +9105,53 @@
       <c r="K211" s="18"/>
     </row>
     <row r="212" spans="1:11" s="42" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="60" t="s">
-        <v>412</v>
-      </c>
-      <c r="B212" s="51"/>
-      <c r="C212" s="51"/>
-      <c r="D212" s="51"/>
-      <c r="E212" s="51"/>
-      <c r="F212" s="51"/>
-      <c r="G212" s="51"/>
-      <c r="H212" s="51"/>
-      <c r="I212" s="51"/>
-      <c r="J212" s="51"/>
-      <c r="K212" s="52"/>
+      <c r="A212" s="72" t="s">
+        <v>406</v>
+      </c>
+      <c r="B212" s="53"/>
+      <c r="C212" s="53"/>
+      <c r="D212" s="53"/>
+      <c r="E212" s="53"/>
+      <c r="F212" s="53"/>
+      <c r="G212" s="53"/>
+      <c r="H212" s="53"/>
+      <c r="I212" s="53"/>
+      <c r="J212" s="53"/>
+      <c r="K212" s="54"/>
     </row>
     <row r="213" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A213" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B213" s="53" t="s">
-        <v>434</v>
-      </c>
-      <c r="C213" s="51"/>
-      <c r="D213" s="51"/>
-      <c r="E213" s="51"/>
-      <c r="F213" s="51"/>
-      <c r="G213" s="51"/>
-      <c r="H213" s="51"/>
-      <c r="I213" s="51"/>
-      <c r="J213" s="51"/>
-      <c r="K213" s="52"/>
+      <c r="B213" s="73" t="s">
+        <v>428</v>
+      </c>
+      <c r="C213" s="53"/>
+      <c r="D213" s="53"/>
+      <c r="E213" s="53"/>
+      <c r="F213" s="53"/>
+      <c r="G213" s="53"/>
+      <c r="H213" s="53"/>
+      <c r="I213" s="53"/>
+      <c r="J213" s="53"/>
+      <c r="K213" s="54"/>
     </row>
     <row r="214" spans="1:11" s="42" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B214" s="53" t="s">
-        <v>435</v>
-      </c>
-      <c r="C214" s="51"/>
-      <c r="D214" s="51"/>
-      <c r="E214" s="51"/>
-      <c r="F214" s="51"/>
-      <c r="G214" s="51"/>
-      <c r="H214" s="51"/>
-      <c r="I214" s="51"/>
-      <c r="J214" s="51"/>
-      <c r="K214" s="52"/>
+      <c r="B214" s="73" t="s">
+        <v>429</v>
+      </c>
+      <c r="C214" s="53"/>
+      <c r="D214" s="53"/>
+      <c r="E214" s="53"/>
+      <c r="F214" s="53"/>
+      <c r="G214" s="53"/>
+      <c r="H214" s="53"/>
+      <c r="I214" s="53"/>
+      <c r="J214" s="53"/>
+      <c r="K214" s="54"/>
     </row>
     <row r="215" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A215" s="46">
@@ -9159,10 +9161,10 @@
         <v>59</v>
       </c>
       <c r="C215" s="43" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="D215" s="44" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="E215" s="44" t="s">
         <v>68</v>
@@ -9181,7 +9183,7 @@
         <v>0</v>
       </c>
       <c r="J215" s="44" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="K215" s="47"/>
     </row>
@@ -9193,10 +9195,10 @@
         <v>59</v>
       </c>
       <c r="C216" s="43" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="D216" s="44" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="E216" s="44" t="s">
         <v>48</v>
@@ -9215,7 +9217,7 @@
         <v>0</v>
       </c>
       <c r="J216" s="44" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="K216" s="47"/>
     </row>
@@ -9227,10 +9229,10 @@
         <v>59</v>
       </c>
       <c r="C217" s="43" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D217" s="44" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E217" s="44" t="s">
         <v>68</v>
@@ -9249,7 +9251,7 @@
         <v>0</v>
       </c>
       <c r="J217" s="44" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="K217" s="47"/>
     </row>
@@ -9261,10 +9263,10 @@
         <v>59</v>
       </c>
       <c r="C218" s="43" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D218" s="44" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E218" s="44" t="s">
         <v>68</v>
@@ -9283,7 +9285,7 @@
         <v>0</v>
       </c>
       <c r="J218" s="44" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="K218" s="47"/>
     </row>
@@ -9295,10 +9297,10 @@
         <v>59</v>
       </c>
       <c r="C219" s="43" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D219" s="44" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="E219" s="44" t="s">
         <v>68</v>
@@ -9317,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="J219" s="44" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="K219" s="47"/>
     </row>
@@ -9329,10 +9331,10 @@
         <v>59</v>
       </c>
       <c r="C220" s="43" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D220" s="44" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="E220" s="44" t="s">
         <v>68</v>
@@ -9351,7 +9353,7 @@
         <v>0</v>
       </c>
       <c r="J220" s="44" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="K220" s="47"/>
     </row>
@@ -9363,10 +9365,10 @@
         <v>59</v>
       </c>
       <c r="C221" s="48" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D221" s="39" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="E221" s="39" t="s">
         <v>66</v>
@@ -9386,7 +9388,7 @@
       </c>
       <c r="J221" s="44"/>
       <c r="K221" s="47" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="222" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -9397,10 +9399,10 @@
         <v>59</v>
       </c>
       <c r="C222" s="43" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D222" s="44" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="E222" s="44" t="s">
         <v>48</v>
@@ -9419,7 +9421,7 @@
         <v>0</v>
       </c>
       <c r="J222" s="44" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="K222" s="47"/>
     </row>
@@ -9431,10 +9433,10 @@
         <v>59</v>
       </c>
       <c r="C223" s="43" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="D223" s="44" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="E223" s="44" t="s">
         <v>60</v>
@@ -9480,53 +9482,53 @@
       <c r="K224" s="18"/>
     </row>
     <row r="225" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A225" s="54" t="s">
-        <v>413</v>
-      </c>
-      <c r="B225" s="51"/>
-      <c r="C225" s="51"/>
-      <c r="D225" s="51"/>
-      <c r="E225" s="51"/>
-      <c r="F225" s="51"/>
-      <c r="G225" s="51"/>
-      <c r="H225" s="51"/>
-      <c r="I225" s="51"/>
-      <c r="J225" s="51"/>
-      <c r="K225" s="52"/>
+      <c r="A225" s="65" t="s">
+        <v>407</v>
+      </c>
+      <c r="B225" s="53"/>
+      <c r="C225" s="53"/>
+      <c r="D225" s="53"/>
+      <c r="E225" s="53"/>
+      <c r="F225" s="53"/>
+      <c r="G225" s="53"/>
+      <c r="H225" s="53"/>
+      <c r="I225" s="53"/>
+      <c r="J225" s="53"/>
+      <c r="K225" s="54"/>
     </row>
     <row r="226" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A226" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B226" s="55" t="s">
-        <v>458</v>
-      </c>
-      <c r="C226" s="56"/>
-      <c r="D226" s="56"/>
-      <c r="E226" s="56"/>
-      <c r="F226" s="56"/>
-      <c r="G226" s="56"/>
-      <c r="H226" s="56"/>
-      <c r="I226" s="56"/>
-      <c r="J226" s="56"/>
-      <c r="K226" s="57"/>
+      <c r="B226" s="76" t="s">
+        <v>452</v>
+      </c>
+      <c r="C226" s="51"/>
+      <c r="D226" s="51"/>
+      <c r="E226" s="51"/>
+      <c r="F226" s="51"/>
+      <c r="G226" s="51"/>
+      <c r="H226" s="51"/>
+      <c r="I226" s="51"/>
+      <c r="J226" s="51"/>
+      <c r="K226" s="77"/>
     </row>
     <row r="227" spans="1:11" s="42" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="B227" s="58" t="s">
-        <v>459</v>
-      </c>
-      <c r="C227" s="56"/>
-      <c r="D227" s="56"/>
-      <c r="E227" s="56"/>
-      <c r="F227" s="56"/>
-      <c r="G227" s="56"/>
-      <c r="H227" s="56"/>
-      <c r="I227" s="56"/>
-      <c r="J227" s="56"/>
-      <c r="K227" s="57"/>
+      <c r="B227" s="78" t="s">
+        <v>453</v>
+      </c>
+      <c r="C227" s="51"/>
+      <c r="D227" s="51"/>
+      <c r="E227" s="51"/>
+      <c r="F227" s="51"/>
+      <c r="G227" s="51"/>
+      <c r="H227" s="51"/>
+      <c r="I227" s="51"/>
+      <c r="J227" s="51"/>
+      <c r="K227" s="77"/>
     </row>
     <row r="228" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A228" s="46">
@@ -9536,10 +9538,10 @@
         <v>59</v>
       </c>
       <c r="C228" s="43" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="D228" s="44" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="E228" s="44" t="s">
         <v>68</v>
@@ -9558,7 +9560,7 @@
         <v>0</v>
       </c>
       <c r="J228" s="44" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="K228" s="47"/>
     </row>
@@ -9570,10 +9572,10 @@
         <v>59</v>
       </c>
       <c r="C229" s="43" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D229" s="44" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="E229" s="44" t="s">
         <v>68</v>
@@ -9592,7 +9594,7 @@
         <v>0</v>
       </c>
       <c r="J229" s="44" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K229" s="47"/>
     </row>
@@ -9604,10 +9606,10 @@
         <v>59</v>
       </c>
       <c r="C230" s="43" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="D230" s="44" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="E230" s="44" t="s">
         <v>68</v>
@@ -9626,7 +9628,7 @@
         <v>0</v>
       </c>
       <c r="J230" s="44" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="K230" s="47"/>
     </row>
@@ -9638,10 +9640,10 @@
         <v>59</v>
       </c>
       <c r="C231" s="43" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="D231" s="44" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="E231" s="44" t="s">
         <v>68</v>
@@ -9660,7 +9662,7 @@
         <v>0</v>
       </c>
       <c r="J231" s="44" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="K231" s="47"/>
     </row>
@@ -9672,10 +9674,10 @@
         <v>59</v>
       </c>
       <c r="C232" s="43" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="D232" s="44" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="E232" s="44" t="s">
         <v>68</v>
@@ -9694,7 +9696,7 @@
         <v>0</v>
       </c>
       <c r="J232" s="44" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="K232" s="47"/>
     </row>
@@ -9706,10 +9708,10 @@
         <v>59</v>
       </c>
       <c r="C233" s="43" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="D233" s="44" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="E233" s="44" t="s">
         <v>68</v>
@@ -9728,7 +9730,7 @@
         <v>0</v>
       </c>
       <c r="J233" s="44" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="K233" s="47"/>
     </row>
@@ -9740,10 +9742,10 @@
         <v>59</v>
       </c>
       <c r="C234" s="48" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D234" s="39" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="E234" s="39" t="s">
         <v>66</v>
@@ -9763,7 +9765,7 @@
       </c>
       <c r="J234" s="44"/>
       <c r="K234" s="47" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
     </row>
     <row r="235" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -9774,10 +9776,10 @@
         <v>59</v>
       </c>
       <c r="C235" s="43" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="D235" s="44" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="E235" s="44" t="s">
         <v>68</v>
@@ -9796,7 +9798,7 @@
         <v>0</v>
       </c>
       <c r="J235" s="44" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K235" s="47"/>
     </row>
@@ -9808,10 +9810,10 @@
         <v>59</v>
       </c>
       <c r="C236" s="43" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="D236" s="44" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="E236" s="44" t="s">
         <v>60</v>
@@ -9857,53 +9859,53 @@
       <c r="K237" s="18"/>
     </row>
     <row r="238" spans="1:11" s="42" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A238" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="B238" s="51"/>
-      <c r="C238" s="51"/>
-      <c r="D238" s="51"/>
-      <c r="E238" s="51"/>
-      <c r="F238" s="51"/>
-      <c r="G238" s="51"/>
-      <c r="H238" s="51"/>
-      <c r="I238" s="51"/>
-      <c r="J238" s="51"/>
-      <c r="K238" s="52"/>
+      <c r="A238" s="74" t="s">
+        <v>408</v>
+      </c>
+      <c r="B238" s="53"/>
+      <c r="C238" s="53"/>
+      <c r="D238" s="53"/>
+      <c r="E238" s="53"/>
+      <c r="F238" s="53"/>
+      <c r="G238" s="53"/>
+      <c r="H238" s="53"/>
+      <c r="I238" s="53"/>
+      <c r="J238" s="53"/>
+      <c r="K238" s="54"/>
     </row>
     <row r="239" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A239" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B239" s="50" t="s">
-        <v>482</v>
-      </c>
-      <c r="C239" s="51"/>
-      <c r="D239" s="51"/>
-      <c r="E239" s="51"/>
-      <c r="F239" s="51"/>
-      <c r="G239" s="51"/>
-      <c r="H239" s="51"/>
-      <c r="I239" s="51"/>
-      <c r="J239" s="51"/>
-      <c r="K239" s="52"/>
+      <c r="B239" s="75" t="s">
+        <v>476</v>
+      </c>
+      <c r="C239" s="53"/>
+      <c r="D239" s="53"/>
+      <c r="E239" s="53"/>
+      <c r="F239" s="53"/>
+      <c r="G239" s="53"/>
+      <c r="H239" s="53"/>
+      <c r="I239" s="53"/>
+      <c r="J239" s="53"/>
+      <c r="K239" s="54"/>
     </row>
     <row r="240" spans="1:11" s="42" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B240" s="50" t="s">
-        <v>483</v>
-      </c>
-      <c r="C240" s="51"/>
-      <c r="D240" s="51"/>
-      <c r="E240" s="51"/>
-      <c r="F240" s="51"/>
-      <c r="G240" s="51"/>
-      <c r="H240" s="51"/>
-      <c r="I240" s="51"/>
-      <c r="J240" s="51"/>
-      <c r="K240" s="52"/>
+      <c r="B240" s="75" t="s">
+        <v>477</v>
+      </c>
+      <c r="C240" s="53"/>
+      <c r="D240" s="53"/>
+      <c r="E240" s="53"/>
+      <c r="F240" s="53"/>
+      <c r="G240" s="53"/>
+      <c r="H240" s="53"/>
+      <c r="I240" s="53"/>
+      <c r="J240" s="53"/>
+      <c r="K240" s="54"/>
     </row>
     <row r="241" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A241" s="46">
@@ -9913,10 +9915,10 @@
         <v>59</v>
       </c>
       <c r="C241" s="43" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="D241" s="44" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E241" s="44" t="s">
         <v>68</v>
@@ -9935,7 +9937,7 @@
         <v>0</v>
       </c>
       <c r="J241" s="44" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="K241" s="47"/>
     </row>
@@ -9947,10 +9949,10 @@
         <v>59</v>
       </c>
       <c r="C242" s="43" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="D242" s="44" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="E242" s="44" t="s">
         <v>68</v>
@@ -9969,7 +9971,7 @@
         <v>0</v>
       </c>
       <c r="J242" s="44" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="K242" s="47"/>
     </row>
@@ -9981,10 +9983,10 @@
         <v>59</v>
       </c>
       <c r="C243" s="43" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="D243" s="44" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="E243" s="44" t="s">
         <v>68</v>
@@ -10003,7 +10005,7 @@
         <v>0</v>
       </c>
       <c r="J243" s="44" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="K243" s="47"/>
     </row>
@@ -10015,10 +10017,10 @@
         <v>59</v>
       </c>
       <c r="C244" s="43" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="D244" s="44" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="E244" s="44" t="s">
         <v>68</v>
@@ -10037,7 +10039,7 @@
         <v>0</v>
       </c>
       <c r="J244" s="44" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="K244" s="47"/>
     </row>
@@ -10049,10 +10051,10 @@
         <v>59</v>
       </c>
       <c r="C245" s="43" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D245" s="44" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="E245" s="44" t="s">
         <v>68</v>
@@ -10081,10 +10083,10 @@
         <v>59</v>
       </c>
       <c r="C246" s="43" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="D246" s="44" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="E246" s="44" t="s">
         <v>68</v>
@@ -10103,7 +10105,7 @@
         <v>0</v>
       </c>
       <c r="J246" s="44" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="K246" s="47"/>
     </row>
@@ -10115,10 +10117,10 @@
         <v>59</v>
       </c>
       <c r="C247" s="43" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="D247" s="44" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="E247" s="44" t="s">
         <v>68</v>
@@ -10147,10 +10149,10 @@
         <v>59</v>
       </c>
       <c r="C248" s="43" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="D248" s="44" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="E248" s="44" t="s">
         <v>68</v>
@@ -10179,10 +10181,10 @@
         <v>59</v>
       </c>
       <c r="C249" s="43" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="D249" s="44" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="E249" s="44" t="s">
         <v>68</v>
@@ -10211,10 +10213,10 @@
         <v>59</v>
       </c>
       <c r="C250" s="48" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D250" s="39" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="E250" s="39" t="s">
         <v>66</v>
@@ -10234,7 +10236,7 @@
       </c>
       <c r="J250" s="44"/>
       <c r="K250" s="47" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
     </row>
     <row r="251" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -10245,10 +10247,10 @@
         <v>59</v>
       </c>
       <c r="C251" s="43" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="D251" s="44" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="E251" s="44" t="s">
         <v>60</v>
@@ -10334,21 +10336,42 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="60">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="B16:K16"/>
-    <mergeCell ref="B17:K17"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="B28:K28"/>
-    <mergeCell ref="B29:K29"/>
-    <mergeCell ref="A39:K39"/>
-    <mergeCell ref="B40:K40"/>
-    <mergeCell ref="B41:K41"/>
-    <mergeCell ref="A52:K52"/>
-    <mergeCell ref="B53:K53"/>
-    <mergeCell ref="A89:K89"/>
+    <mergeCell ref="B239:K239"/>
+    <mergeCell ref="B240:K240"/>
+    <mergeCell ref="B214:K214"/>
+    <mergeCell ref="A225:K225"/>
+    <mergeCell ref="B226:K226"/>
+    <mergeCell ref="B227:K227"/>
+    <mergeCell ref="A238:K238"/>
+    <mergeCell ref="A200:K200"/>
+    <mergeCell ref="B201:K201"/>
+    <mergeCell ref="B202:K202"/>
+    <mergeCell ref="A212:K212"/>
+    <mergeCell ref="B213:K213"/>
+    <mergeCell ref="B176:K176"/>
+    <mergeCell ref="A187:K187"/>
+    <mergeCell ref="B188:K188"/>
+    <mergeCell ref="B189:K189"/>
+    <mergeCell ref="A162:K162"/>
+    <mergeCell ref="B163:K163"/>
+    <mergeCell ref="B164:K164"/>
+    <mergeCell ref="A174:K174"/>
+    <mergeCell ref="B175:K175"/>
+    <mergeCell ref="B139:K139"/>
+    <mergeCell ref="B140:K140"/>
+    <mergeCell ref="A151:K151"/>
+    <mergeCell ref="B152:K152"/>
+    <mergeCell ref="B153:K153"/>
+    <mergeCell ref="B116:K116"/>
+    <mergeCell ref="A127:K127"/>
+    <mergeCell ref="B128:K128"/>
+    <mergeCell ref="B129:K129"/>
+    <mergeCell ref="A138:K138"/>
+    <mergeCell ref="A102:K102"/>
+    <mergeCell ref="B103:K103"/>
+    <mergeCell ref="B104:K104"/>
+    <mergeCell ref="A114:K114"/>
+    <mergeCell ref="B115:K115"/>
     <mergeCell ref="B90:K90"/>
     <mergeCell ref="B91:K91"/>
     <mergeCell ref="B54:K54"/>
@@ -10358,42 +10381,21 @@
     <mergeCell ref="A77:K77"/>
     <mergeCell ref="B78:K78"/>
     <mergeCell ref="B79:K79"/>
-    <mergeCell ref="A102:K102"/>
-    <mergeCell ref="B103:K103"/>
-    <mergeCell ref="B104:K104"/>
-    <mergeCell ref="A114:K114"/>
-    <mergeCell ref="B115:K115"/>
-    <mergeCell ref="B116:K116"/>
-    <mergeCell ref="A127:K127"/>
-    <mergeCell ref="B128:K128"/>
-    <mergeCell ref="B129:K129"/>
-    <mergeCell ref="A138:K138"/>
-    <mergeCell ref="B139:K139"/>
-    <mergeCell ref="B140:K140"/>
-    <mergeCell ref="A151:K151"/>
-    <mergeCell ref="B152:K152"/>
-    <mergeCell ref="B153:K153"/>
-    <mergeCell ref="B176:K176"/>
-    <mergeCell ref="A187:K187"/>
-    <mergeCell ref="B188:K188"/>
-    <mergeCell ref="B189:K189"/>
-    <mergeCell ref="A162:K162"/>
-    <mergeCell ref="B163:K163"/>
-    <mergeCell ref="B164:K164"/>
-    <mergeCell ref="A174:K174"/>
-    <mergeCell ref="B175:K175"/>
-    <mergeCell ref="A200:K200"/>
-    <mergeCell ref="B201:K201"/>
-    <mergeCell ref="B202:K202"/>
-    <mergeCell ref="A212:K212"/>
-    <mergeCell ref="B213:K213"/>
-    <mergeCell ref="B239:K239"/>
-    <mergeCell ref="B240:K240"/>
-    <mergeCell ref="B214:K214"/>
-    <mergeCell ref="A225:K225"/>
-    <mergeCell ref="B226:K226"/>
-    <mergeCell ref="B227:K227"/>
-    <mergeCell ref="A238:K238"/>
+    <mergeCell ref="B40:K40"/>
+    <mergeCell ref="B41:K41"/>
+    <mergeCell ref="A52:K52"/>
+    <mergeCell ref="B53:K53"/>
+    <mergeCell ref="A89:K89"/>
+    <mergeCell ref="B17:K17"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="B28:K28"/>
+    <mergeCell ref="B29:K29"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="B16:K16"/>
   </mergeCells>
   <conditionalFormatting sqref="B16:B25 B30:B37 B42:B50 B55:B62 B67:B75 B80:B87 B92:B98 B190:B198 B5:B13">
     <cfRule type="containsText" dxfId="69" priority="78" operator="containsText" text="Unplanned">
@@ -10669,8 +10671,27 @@
       <formula>H254/G254&lt;=0.5</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="J5" r:id="rId1"/>
+    <hyperlink ref="J6" r:id="rId2"/>
+    <hyperlink ref="J7" r:id="rId3"/>
+    <hyperlink ref="J8" r:id="rId4"/>
+    <hyperlink ref="J9" r:id="rId5"/>
+    <hyperlink ref="J10" r:id="rId6"/>
+    <hyperlink ref="J19" r:id="rId7"/>
+    <hyperlink ref="J20" r:id="rId8"/>
+    <hyperlink ref="J21" r:id="rId9"/>
+    <hyperlink ref="J18" r:id="rId10"/>
+    <hyperlink ref="J22" r:id="rId11"/>
+    <hyperlink ref="J23" r:id="rId12"/>
+    <hyperlink ref="J31" r:id="rId13"/>
+    <hyperlink ref="J30" r:id="rId14"/>
+    <hyperlink ref="J32" r:id="rId15"/>
+    <hyperlink ref="J33" r:id="rId16"/>
+    <hyperlink ref="J34" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId18"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -12150,17 +12171,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5ff92c65-ed86-4457-baee-ccd535c9ea21">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6c8d291c-a5bf-4049-930d-38db8e991d8e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000BADAD4AA324BF48804EF76FD903323C" ma:contentTypeVersion="15" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="fe102fc92a60fb44f88498837809608c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5ff92c65-ed86-4457-baee-ccd535c9ea21" xmlns:ns3="6c8d291c-a5bf-4049-930d-38db8e991d8e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="02f72fefe31d96546aeabc284eee7b20" ns2:_="" ns3:_="">
     <xsd:import namespace="5ff92c65-ed86-4457-baee-ccd535c9ea21"/>
@@ -12395,6 +12405,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5ff92c65-ed86-4457-baee-ccd535c9ea21">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6c8d291c-a5bf-4049-930d-38db8e991d8e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -12405,17 +12426,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{320CF63A-30C9-4A8C-8DF9-EA62B8EC1A62}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5ff92c65-ed86-4457-baee-ccd535c9ea21"/>
-    <ds:schemaRef ds:uri="6c8d291c-a5bf-4049-930d-38db8e991d8e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0601B52F-B381-4AF0-AEAA-A07715E93BF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12434,6 +12444,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{320CF63A-30C9-4A8C-8DF9-EA62B8EC1A62}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5ff92c65-ed86-4457-baee-ccd535c9ea21"/>
+    <ds:schemaRef ds:uri="6c8d291c-a5bf-4049-930d-38db8e991d8e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67A64A65-7DA4-4AE1-9847-B817073E4705}">
   <ds:schemaRefs>

--- a/thesis/evidencing/ADS&AI Work Log Graduation Project.xlsx
+++ b/thesis/evidencing/ADS&AI Work Log Graduation Project.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="526">
   <si>
     <t>Date</t>
   </si>
@@ -458,9 +458,6 @@
     <t>First full run</t>
   </si>
   <si>
-    <t>runs/</t>
-  </si>
-  <si>
     <t>Train Faster R-CNN on small dataset</t>
   </si>
   <si>
@@ -581,9 +578,6 @@
     <t>Test reload speed</t>
   </si>
   <si>
-    <t>src/geospatial/</t>
-  </si>
-  <si>
     <t>Implement GPS-to-edge matching</t>
   </si>
   <si>
@@ -614,9 +608,6 @@
     <t>Script-level test</t>
   </si>
   <si>
-    <t>src/routing/</t>
-  </si>
-  <si>
     <t>Confirm the full chain works end to end (script)</t>
   </si>
   <si>
@@ -641,9 +632,6 @@
     <t>Shared config loading</t>
   </si>
   <si>
-    <t>app.py, pages/</t>
-  </si>
-  <si>
     <t>Build Upload and Detect page</t>
   </si>
   <si>
@@ -743,9 +731,6 @@
     <t>Second dataset scale</t>
   </si>
   <si>
-    <t>data/processed/medium/</t>
-  </si>
-  <si>
     <t>Train YOLOv8n on medium dataset</t>
   </si>
   <si>
@@ -794,9 +779,6 @@
     <t>4,291/597/592</t>
   </si>
   <si>
-    <t>data/processed/large/</t>
-  </si>
-  <si>
     <t>Verify balancing output</t>
   </si>
   <si>
@@ -827,9 +809,6 @@
     <t>Train Faster R-CNN on large dataset</t>
   </si>
   <si>
-    <t>models/fasterrcnn_large/</t>
-  </si>
-  <si>
     <t>Debug FRCNN GPU memory error, resume training</t>
   </si>
   <si>
@@ -1217,9 +1196,6 @@
     <t>Trace causes of under-scoring</t>
   </si>
   <si>
-    <t>thesis 4.1.4</t>
-  </si>
-  <si>
     <t>Draft H2/H3/H4 results notes</t>
   </si>
   <si>
@@ -1319,18 +1295,12 @@
     <t>Full sample</t>
   </si>
   <si>
-    <t>outputs/reports/qualitative_survey_means_n10.png</t>
-  </si>
-  <si>
     <t>Code open-ended responses into 7 themes (full n=10)</t>
   </si>
   <si>
     <t>Final thematic coding</t>
   </si>
   <si>
-    <t>thesis/qualitative_thematic_analysis.md</t>
-  </si>
-  <si>
     <t>Full pipeline smoke test end to end</t>
   </si>
   <si>
@@ -1343,9 +1313,6 @@
     <t>Final values locked</t>
   </si>
   <si>
-    <t>models/, config/</t>
-  </si>
-  <si>
     <t>Capture final application screenshots</t>
   </si>
   <si>
@@ -1610,9 +1577,6 @@
     <t>We discussed the whole structure of the thesi and section ordering and formatting</t>
   </si>
   <si>
-    <t>I demoed the app to the supervisor and got feedback that everything works fine by now, but have to ellaborate everything in the thesis.</t>
-  </si>
-  <si>
     <t>visual dataset inspection notebook</t>
   </si>
   <si>
@@ -1626,6 +1590,60 @@
   </si>
   <si>
     <t>first FasteRNN training</t>
+  </si>
+  <si>
+    <t>Product architecture plan</t>
+  </si>
+  <si>
+    <t>src/risk/scoring.py</t>
+  </si>
+  <si>
+    <t>src/geospatial/matching.py</t>
+  </si>
+  <si>
+    <t>app.py</t>
+  </si>
+  <si>
+    <t>Classes visual inspection</t>
+  </si>
+  <si>
+    <t>Yolo_medium_data_train</t>
+  </si>
+  <si>
+    <t>Fasterrcnn_medium_dataset_train</t>
+  </si>
+  <si>
+    <t>Evaluation images in notebooks, and saved in the notebooks/ folder</t>
+  </si>
+  <si>
+    <t>scripts/create_rdd2022_4classes_large.py</t>
+  </si>
+  <si>
+    <t>YoLo_large_dataset_train</t>
+  </si>
+  <si>
+    <t>Faster RNN large dataset train</t>
+  </si>
+  <si>
+    <t>H4 evaluation</t>
+  </si>
+  <si>
+    <t>H2 evaluation</t>
+  </si>
+  <si>
+    <t>Qualitative Survey Question and Responses</t>
+  </si>
+  <si>
+    <t>thematic analysis</t>
+  </si>
+  <si>
+    <t>I showed the app to the supervisor and got feedback that everything works fine by now, but have to ellaborate everything in the thesis.</t>
+  </si>
+  <si>
+    <t>analyze_qualitative_survey.py</t>
+  </si>
+  <si>
+    <t>models/</t>
   </si>
 </sst>
 </file>
@@ -3395,10 +3413,10 @@
         <v>59</v>
       </c>
       <c r="C11" s="48" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="E11" s="39" t="s">
         <v>66</v>
@@ -3586,7 +3604,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="82" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="K18" s="24"/>
     </row>
@@ -3620,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="82" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="K19" s="24"/>
     </row>
@@ -3722,7 +3740,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="82" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="K22" s="24"/>
     </row>
@@ -3756,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="82" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="K23" s="24"/>
     </row>
@@ -3868,7 +3886,7 @@
         <v>12</v>
       </c>
       <c r="B28" s="58" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C28" s="53"/>
       <c r="D28" s="53"/>
@@ -3885,7 +3903,7 @@
         <v>13</v>
       </c>
       <c r="B29" s="58" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C29" s="53"/>
       <c r="D29" s="53"/>
@@ -3927,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="82" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="K30" s="24"/>
     </row>
@@ -3961,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="82" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="K31" s="24"/>
     </row>
@@ -3995,7 +4013,7 @@
         <v>0.5</v>
       </c>
       <c r="J32" s="82" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="K32" s="24"/>
     </row>
@@ -4029,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="82" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="K33" s="24"/>
     </row>
@@ -4041,7 +4059,7 @@
         <v>59</v>
       </c>
       <c r="C34" s="43" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D34" s="44" t="s">
         <v>129</v>
@@ -4063,7 +4081,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="82" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="K34" s="24"/>
     </row>
@@ -4075,10 +4093,10 @@
         <v>59</v>
       </c>
       <c r="C35" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="D35" s="44" t="s">
         <v>132</v>
-      </c>
-      <c r="D35" s="44" t="s">
-        <v>133</v>
       </c>
       <c r="E35" s="44" t="s">
         <v>60</v>
@@ -4096,9 +4114,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J35" s="44" t="s">
-        <v>134</v>
-      </c>
+      <c r="J35" s="44"/>
       <c r="K35" s="24"/>
     </row>
     <row r="36" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -4109,10 +4125,10 @@
         <v>59</v>
       </c>
       <c r="C36" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="44" t="s">
         <v>135</v>
-      </c>
-      <c r="D36" s="44" t="s">
-        <v>136</v>
       </c>
       <c r="E36" s="44" t="s">
         <v>74</v>
@@ -4141,10 +4157,10 @@
         <v>59</v>
       </c>
       <c r="C37" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="D37" s="44" t="s">
         <v>137</v>
-      </c>
-      <c r="D37" s="44" t="s">
-        <v>138</v>
       </c>
       <c r="E37" s="44" t="s">
         <v>48</v>
@@ -4162,8 +4178,8 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J37" s="44" t="s">
-        <v>139</v>
+      <c r="J37" s="82" t="s">
+        <v>508</v>
       </c>
       <c r="K37" s="24"/>
     </row>
@@ -4211,7 +4227,7 @@
         <v>12</v>
       </c>
       <c r="B40" s="60" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C40" s="53"/>
       <c r="D40" s="53"/>
@@ -4228,7 +4244,7 @@
         <v>13</v>
       </c>
       <c r="B41" s="60" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C41" s="53"/>
       <c r="D41" s="53"/>
@@ -4248,10 +4264,10 @@
         <v>59</v>
       </c>
       <c r="C42" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="D42" s="44" t="s">
         <v>144</v>
-      </c>
-      <c r="D42" s="44" t="s">
-        <v>145</v>
       </c>
       <c r="E42" s="44" t="s">
         <v>48</v>
@@ -4269,8 +4285,8 @@
         <f t="shared" ref="I42:I50" si="6">H42-G42</f>
         <v>0</v>
       </c>
-      <c r="J42" s="44" t="s">
-        <v>146</v>
+      <c r="J42" s="82" t="s">
+        <v>145</v>
       </c>
       <c r="K42" s="24"/>
     </row>
@@ -4282,10 +4298,10 @@
         <v>59</v>
       </c>
       <c r="C43" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43" s="44" t="s">
         <v>147</v>
-      </c>
-      <c r="D43" s="44" t="s">
-        <v>148</v>
       </c>
       <c r="E43" s="44" t="s">
         <v>48</v>
@@ -4303,8 +4319,8 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J43" s="44" t="s">
-        <v>146</v>
+      <c r="J43" s="82" t="s">
+        <v>145</v>
       </c>
       <c r="K43" s="24"/>
     </row>
@@ -4316,10 +4332,10 @@
         <v>59</v>
       </c>
       <c r="C44" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="D44" s="44" t="s">
         <v>149</v>
-      </c>
-      <c r="D44" s="44" t="s">
-        <v>150</v>
       </c>
       <c r="E44" s="44" t="s">
         <v>48</v>
@@ -4337,8 +4353,8 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J44" s="44" t="s">
-        <v>146</v>
+      <c r="J44" s="82" t="s">
+        <v>145</v>
       </c>
       <c r="K44" s="24"/>
     </row>
@@ -4350,10 +4366,10 @@
         <v>59</v>
       </c>
       <c r="C45" s="43" t="s">
+        <v>150</v>
+      </c>
+      <c r="D45" s="44" t="s">
         <v>151</v>
-      </c>
-      <c r="D45" s="44" t="s">
-        <v>152</v>
       </c>
       <c r="E45" s="44" t="s">
         <v>57</v>
@@ -4371,8 +4387,8 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J45" s="44" t="s">
-        <v>146</v>
+      <c r="J45" s="82" t="s">
+        <v>145</v>
       </c>
       <c r="K45" s="24"/>
     </row>
@@ -4384,10 +4400,10 @@
         <v>59</v>
       </c>
       <c r="C46" s="48" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="D46" s="44" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="E46" s="39" t="s">
         <v>66</v>
@@ -4416,10 +4432,10 @@
         <v>59</v>
       </c>
       <c r="C47" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="D47" s="44" t="s">
         <v>153</v>
-      </c>
-      <c r="D47" s="44" t="s">
-        <v>154</v>
       </c>
       <c r="E47" s="44" t="s">
         <v>54</v>
@@ -4437,8 +4453,8 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J47" s="44" t="s">
-        <v>155</v>
+      <c r="J47" s="82" t="s">
+        <v>154</v>
       </c>
       <c r="K47" s="24"/>
     </row>
@@ -4450,10 +4466,10 @@
         <v>59</v>
       </c>
       <c r="C48" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="D48" s="44" t="s">
         <v>156</v>
-      </c>
-      <c r="D48" s="44" t="s">
-        <v>157</v>
       </c>
       <c r="E48" s="44" t="s">
         <v>54</v>
@@ -4471,8 +4487,8 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J48" s="44" t="s">
-        <v>158</v>
+      <c r="J48" s="82" t="s">
+        <v>509</v>
       </c>
       <c r="K48" s="24"/>
     </row>
@@ -4484,10 +4500,10 @@
         <v>59</v>
       </c>
       <c r="C49" s="43" t="s">
+        <v>158</v>
+      </c>
+      <c r="D49" s="44" t="s">
         <v>159</v>
-      </c>
-      <c r="D49" s="44" t="s">
-        <v>160</v>
       </c>
       <c r="E49" s="44" t="s">
         <v>54</v>
@@ -4505,8 +4521,8 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J49" s="44" t="s">
-        <v>161</v>
+      <c r="J49" s="82" t="s">
+        <v>160</v>
       </c>
       <c r="K49" s="24"/>
     </row>
@@ -4518,10 +4534,10 @@
         <v>59</v>
       </c>
       <c r="C50" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="D50" s="44" t="s">
         <v>162</v>
-      </c>
-      <c r="D50" s="44" t="s">
-        <v>163</v>
       </c>
       <c r="E50" s="44" t="s">
         <v>60</v>
@@ -4539,8 +4555,8 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J50" s="44" t="s">
-        <v>158</v>
+      <c r="J50" s="82" t="s">
+        <v>157</v>
       </c>
       <c r="K50" s="24"/>
     </row>
@@ -4588,7 +4604,7 @@
         <v>12</v>
       </c>
       <c r="B53" s="62" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C53" s="63"/>
       <c r="D53" s="63"/>
@@ -4605,7 +4621,7 @@
         <v>13</v>
       </c>
       <c r="B54" s="62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C54" s="63"/>
       <c r="D54" s="63"/>
@@ -4625,10 +4641,10 @@
         <v>59</v>
       </c>
       <c r="C55" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="D55" s="44" t="s">
         <v>166</v>
-      </c>
-      <c r="D55" s="44" t="s">
-        <v>167</v>
       </c>
       <c r="E55" s="44" t="s">
         <v>54</v>
@@ -4646,8 +4662,8 @@
         <f t="shared" ref="I55:I62" si="8">H55-G55</f>
         <v>0</v>
       </c>
-      <c r="J55" s="44" t="s">
-        <v>168</v>
+      <c r="J55" s="82" t="s">
+        <v>167</v>
       </c>
       <c r="K55" s="24"/>
     </row>
@@ -4659,10 +4675,10 @@
         <v>59</v>
       </c>
       <c r="C56" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="D56" s="44" t="s">
         <v>169</v>
-      </c>
-      <c r="D56" s="44" t="s">
-        <v>170</v>
       </c>
       <c r="E56" s="44" t="s">
         <v>54</v>
@@ -4680,8 +4696,8 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J56" s="44" t="s">
-        <v>171</v>
+      <c r="J56" s="82" t="s">
+        <v>167</v>
       </c>
       <c r="K56" s="24"/>
     </row>
@@ -4693,10 +4709,10 @@
         <v>59</v>
       </c>
       <c r="C57" s="43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D57" s="44" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E57" s="44" t="s">
         <v>54</v>
@@ -4714,8 +4730,8 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J57" s="44" t="s">
-        <v>171</v>
+      <c r="J57" s="82" t="s">
+        <v>510</v>
       </c>
       <c r="K57" s="24"/>
     </row>
@@ -4727,10 +4743,10 @@
         <v>59</v>
       </c>
       <c r="C58" s="43" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D58" s="44" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E58" s="44" t="s">
         <v>54</v>
@@ -4748,8 +4764,8 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J58" s="44" t="s">
-        <v>176</v>
+      <c r="J58" s="82" t="s">
+        <v>174</v>
       </c>
       <c r="K58" s="24"/>
     </row>
@@ -4761,10 +4777,10 @@
         <v>59</v>
       </c>
       <c r="C59" s="43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D59" s="44" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E59" s="44" t="s">
         <v>54</v>
@@ -4782,8 +4798,8 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J59" s="44" t="s">
-        <v>179</v>
+      <c r="J59" s="82" t="s">
+        <v>177</v>
       </c>
       <c r="K59" s="24"/>
     </row>
@@ -4795,10 +4811,10 @@
         <v>59</v>
       </c>
       <c r="C60" s="43" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D60" s="44" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E60" s="44" t="s">
         <v>60</v>
@@ -4816,8 +4832,8 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J60" s="44" t="s">
-        <v>182</v>
+      <c r="J60" s="82" t="s">
+        <v>177</v>
       </c>
       <c r="K60" s="24"/>
     </row>
@@ -4829,10 +4845,10 @@
         <v>59</v>
       </c>
       <c r="C61" s="43" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D61" s="44" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E61" s="44" t="s">
         <v>60</v>
@@ -4861,10 +4877,10 @@
         <v>59</v>
       </c>
       <c r="C62" s="43" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D62" s="44" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E62" s="44" t="s">
         <v>57</v>
@@ -4882,8 +4898,8 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J62" s="44" t="s">
-        <v>155</v>
+      <c r="J62" s="82" t="s">
+        <v>154</v>
       </c>
       <c r="K62" s="24"/>
     </row>
@@ -4931,7 +4947,7 @@
         <v>12</v>
       </c>
       <c r="B65" s="73" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C65" s="53"/>
       <c r="D65" s="53"/>
@@ -4948,7 +4964,7 @@
         <v>13</v>
       </c>
       <c r="B66" s="73" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C66" s="53"/>
       <c r="D66" s="53"/>
@@ -4968,10 +4984,10 @@
         <v>59</v>
       </c>
       <c r="C67" s="43" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D67" s="44" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E67" s="44" t="s">
         <v>54</v>
@@ -4989,8 +5005,8 @@
         <f t="shared" ref="I67:I75" si="10">H67-G67</f>
         <v>0</v>
       </c>
-      <c r="J67" s="44" t="s">
-        <v>191</v>
+      <c r="J67" s="82" t="s">
+        <v>511</v>
       </c>
       <c r="K67" s="47"/>
     </row>
@@ -5002,10 +5018,10 @@
         <v>59</v>
       </c>
       <c r="C68" s="43" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D68" s="44" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E68" s="44" t="s">
         <v>54</v>
@@ -5023,8 +5039,8 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J68" s="44" t="s">
-        <v>194</v>
+      <c r="J68" s="82" t="s">
+        <v>190</v>
       </c>
       <c r="K68" s="47"/>
     </row>
@@ -5036,10 +5052,10 @@
         <v>59</v>
       </c>
       <c r="C69" s="43" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D69" s="44" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E69" s="44" t="s">
         <v>48</v>
@@ -5057,8 +5073,8 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J69" s="44" t="s">
-        <v>197</v>
+      <c r="J69" s="82" t="s">
+        <v>193</v>
       </c>
       <c r="K69" s="47"/>
     </row>
@@ -5070,10 +5086,10 @@
         <v>59</v>
       </c>
       <c r="C70" s="43" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D70" s="44" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E70" s="44" t="s">
         <v>54</v>
@@ -5091,8 +5107,8 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J70" s="44" t="s">
-        <v>200</v>
+      <c r="J70" s="82" t="s">
+        <v>196</v>
       </c>
       <c r="K70" s="47"/>
     </row>
@@ -5104,10 +5120,10 @@
         <v>59</v>
       </c>
       <c r="C71" s="48" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="D71" s="39" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="E71" s="39" t="s">
         <v>66</v>
@@ -5136,10 +5152,10 @@
         <v>59</v>
       </c>
       <c r="C72" s="43" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D72" s="44" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E72" s="44" t="s">
         <v>54</v>
@@ -5157,8 +5173,8 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J72" s="44" t="s">
-        <v>203</v>
+      <c r="J72" s="82" t="s">
+        <v>199</v>
       </c>
       <c r="K72" s="47"/>
     </row>
@@ -5170,10 +5186,10 @@
         <v>59</v>
       </c>
       <c r="C73" s="43" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D73" s="44" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E73" s="44" t="s">
         <v>54</v>
@@ -5191,8 +5207,8 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J73" s="44" t="s">
-        <v>206</v>
+      <c r="J73" s="82" t="s">
+        <v>202</v>
       </c>
       <c r="K73" s="47"/>
     </row>
@@ -5204,10 +5220,10 @@
         <v>59</v>
       </c>
       <c r="C74" s="43" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D74" s="44" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E74" s="44" t="s">
         <v>60</v>
@@ -5225,9 +5241,11 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J74" s="44"/>
+      <c r="J74" s="82" t="s">
+        <v>511</v>
+      </c>
       <c r="K74" s="47" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -5238,10 +5256,10 @@
         <v>59</v>
       </c>
       <c r="C75" s="43" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D75" s="44" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E75" s="44" t="s">
         <v>70</v>
@@ -5259,7 +5277,9 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J75" s="44"/>
+      <c r="J75" s="82" t="s">
+        <v>511</v>
+      </c>
       <c r="K75" s="47"/>
     </row>
     <row r="76" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -5306,7 +5326,7 @@
         <v>12</v>
       </c>
       <c r="B78" s="75" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C78" s="53"/>
       <c r="D78" s="53"/>
@@ -5323,7 +5343,7 @@
         <v>13</v>
       </c>
       <c r="B79" s="75" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C79" s="53"/>
       <c r="D79" s="53"/>
@@ -5343,10 +5363,10 @@
         <v>59</v>
       </c>
       <c r="C80" s="43" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D80" s="44" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E80" s="44" t="s">
         <v>57</v>
@@ -5364,8 +5384,8 @@
         <f t="shared" ref="I80:I87" si="12">H80-G80</f>
         <v>0</v>
       </c>
-      <c r="J80" s="44" t="s">
-        <v>103</v>
+      <c r="J80" s="82" t="s">
+        <v>512</v>
       </c>
       <c r="K80" s="47"/>
     </row>
@@ -5377,10 +5397,10 @@
         <v>59</v>
       </c>
       <c r="C81" s="43" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D81" s="44" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E81" s="44" t="s">
         <v>57</v>
@@ -5398,8 +5418,8 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J81" s="44" t="s">
-        <v>103</v>
+      <c r="J81" s="82" t="s">
+        <v>512</v>
       </c>
       <c r="K81" s="47"/>
     </row>
@@ -5411,10 +5431,10 @@
         <v>59</v>
       </c>
       <c r="C82" s="43" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D82" s="44" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E82" s="44" t="s">
         <v>57</v>
@@ -5432,11 +5452,11 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J82" s="44" t="s">
-        <v>103</v>
+      <c r="J82" s="82" t="s">
+        <v>512</v>
       </c>
       <c r="K82" s="47" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -5447,10 +5467,10 @@
         <v>59</v>
       </c>
       <c r="C83" s="43" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D83" s="44" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E83" s="44" t="s">
         <v>57</v>
@@ -5468,11 +5488,11 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J83" s="44" t="s">
-        <v>103</v>
+      <c r="J83" s="82" t="s">
+        <v>512</v>
       </c>
       <c r="K83" s="47" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -5483,10 +5503,10 @@
         <v>59</v>
       </c>
       <c r="C84" s="43" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D84" s="44" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E84" s="44" t="s">
         <v>54</v>
@@ -5504,8 +5524,8 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J84" s="44" t="s">
-        <v>225</v>
+      <c r="J84" s="82" t="s">
+        <v>504</v>
       </c>
       <c r="K84" s="47"/>
     </row>
@@ -5517,10 +5537,10 @@
         <v>59</v>
       </c>
       <c r="C85" s="43" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D85" s="44" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E85" s="44" t="s">
         <v>54</v>
@@ -5538,8 +5558,8 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J85" s="44" t="s">
-        <v>130</v>
+      <c r="J85" s="82" t="s">
+        <v>513</v>
       </c>
       <c r="K85" s="47"/>
     </row>
@@ -5551,10 +5571,10 @@
         <v>59</v>
       </c>
       <c r="C86" s="43" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D86" s="44" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E86" s="44" t="s">
         <v>54</v>
@@ -5572,8 +5592,8 @@
         <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
-      <c r="J86" s="44" t="s">
-        <v>130</v>
+      <c r="J86" s="82" t="s">
+        <v>514</v>
       </c>
       <c r="K86" s="47"/>
     </row>
@@ -5585,10 +5605,10 @@
         <v>59</v>
       </c>
       <c r="C87" s="43" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D87" s="44" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E87" s="44" t="s">
         <v>60</v>
@@ -5606,8 +5626,8 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J87" s="44" t="s">
-        <v>134</v>
+      <c r="J87" s="82" t="s">
+        <v>515</v>
       </c>
       <c r="K87" s="47"/>
     </row>
@@ -5655,7 +5675,7 @@
         <v>12</v>
       </c>
       <c r="B90" s="66" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C90" s="67"/>
       <c r="D90" s="67"/>
@@ -5672,7 +5692,7 @@
         <v>13</v>
       </c>
       <c r="B91" s="69" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C91" s="70"/>
       <c r="D91" s="70"/>
@@ -5692,10 +5712,10 @@
         <v>59</v>
       </c>
       <c r="C92" s="43" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D92" s="44" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E92" s="44" t="s">
         <v>48</v>
@@ -5713,8 +5733,8 @@
         <f t="shared" ref="I92:I98" si="14">H92-G92</f>
         <v>0</v>
       </c>
-      <c r="J92" s="44" t="s">
-        <v>106</v>
+      <c r="J92" s="82" t="s">
+        <v>516</v>
       </c>
       <c r="K92" s="24"/>
     </row>
@@ -5726,10 +5746,10 @@
         <v>59</v>
       </c>
       <c r="C93" s="43" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D93" s="44" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E93" s="44" t="s">
         <v>54</v>
@@ -5747,8 +5767,8 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J93" s="44" t="s">
-        <v>106</v>
+      <c r="J93" s="82" t="s">
+        <v>516</v>
       </c>
       <c r="K93" s="24"/>
     </row>
@@ -5760,10 +5780,10 @@
         <v>59</v>
       </c>
       <c r="C94" s="43" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D94" s="44" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E94" s="44" t="s">
         <v>54</v>
@@ -5781,8 +5801,8 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J94" s="44" t="s">
-        <v>106</v>
+      <c r="J94" s="82" t="s">
+        <v>516</v>
       </c>
       <c r="K94" s="24"/>
     </row>
@@ -5794,10 +5814,10 @@
         <v>59</v>
       </c>
       <c r="C95" s="43" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D95" s="44" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E95" s="44" t="s">
         <v>60</v>
@@ -5815,8 +5835,8 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J95" s="44" t="s">
-        <v>106</v>
+      <c r="J95" s="82" t="s">
+        <v>516</v>
       </c>
       <c r="K95" s="24"/>
     </row>
@@ -5828,10 +5848,10 @@
         <v>59</v>
       </c>
       <c r="C96" s="43" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D96" s="44" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E96" s="44" t="s">
         <v>54</v>
@@ -5849,8 +5869,8 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J96" s="44" t="s">
-        <v>242</v>
+      <c r="J96" s="82" t="s">
+        <v>504</v>
       </c>
       <c r="K96" s="24"/>
     </row>
@@ -5862,10 +5882,10 @@
         <v>59</v>
       </c>
       <c r="C97" s="43" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D97" s="44" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E97" s="44" t="s">
         <v>60</v>
@@ -5883,8 +5903,8 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J97" s="44" t="s">
-        <v>245</v>
+      <c r="J97" s="82" t="s">
+        <v>239</v>
       </c>
       <c r="K97" s="24"/>
     </row>
@@ -5896,10 +5916,10 @@
         <v>59</v>
       </c>
       <c r="C98" s="43" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D98" s="44" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E98" s="44" t="s">
         <v>54</v>
@@ -5917,8 +5937,8 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J98" s="44" t="s">
-        <v>242</v>
+      <c r="J98" s="82" t="s">
+        <v>504</v>
       </c>
       <c r="K98" s="24"/>
     </row>
@@ -5971,7 +5991,7 @@
         <v>12</v>
       </c>
       <c r="B103" s="52" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C103" s="53"/>
       <c r="D103" s="53"/>
@@ -5988,7 +6008,7 @@
         <v>13</v>
       </c>
       <c r="B104" s="52" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C104" s="53"/>
       <c r="D104" s="53"/>
@@ -6008,10 +6028,10 @@
         <v>59</v>
       </c>
       <c r="C105" s="43" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D105" s="44" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E105" s="44" t="s">
         <v>54</v>
@@ -6029,8 +6049,8 @@
         <f t="shared" ref="I105:I112" si="16">H105-G105</f>
         <v>0</v>
       </c>
-      <c r="J105" s="44" t="s">
-        <v>130</v>
+      <c r="J105" s="82" t="s">
+        <v>517</v>
       </c>
       <c r="K105" s="47"/>
     </row>
@@ -6042,10 +6062,10 @@
         <v>59</v>
       </c>
       <c r="C106" s="43" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D106" s="44" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E106" s="44" t="s">
         <v>54</v>
@@ -6063,8 +6083,8 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J106" s="44" t="s">
-        <v>253</v>
+      <c r="J106" s="82" t="s">
+        <v>518</v>
       </c>
       <c r="K106" s="47"/>
     </row>
@@ -6076,10 +6096,10 @@
         <v>59</v>
       </c>
       <c r="C107" s="43" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D107" s="44" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E107" s="44" t="s">
         <v>70</v>
@@ -6097,8 +6117,8 @@
         <f t="shared" si="16"/>
         <v>0.5</v>
       </c>
-      <c r="J107" s="44" t="s">
-        <v>103</v>
+      <c r="J107" s="82" t="s">
+        <v>518</v>
       </c>
       <c r="K107" s="47"/>
     </row>
@@ -6110,10 +6130,10 @@
         <v>59</v>
       </c>
       <c r="C108" s="43" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D108" s="44" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="E108" s="44" t="s">
         <v>60</v>
@@ -6131,8 +6151,8 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J108" s="44" t="s">
-        <v>134</v>
+      <c r="J108" s="82" t="s">
+        <v>517</v>
       </c>
       <c r="K108" s="47"/>
     </row>
@@ -6144,10 +6164,10 @@
         <v>59</v>
       </c>
       <c r="C109" s="43" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D109" s="44" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="E109" s="44" t="s">
         <v>60</v>
@@ -6165,8 +6185,8 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J109" s="44" t="s">
-        <v>134</v>
+      <c r="J109" s="82" t="s">
+        <v>518</v>
       </c>
       <c r="K109" s="47"/>
     </row>
@@ -6178,10 +6198,10 @@
         <v>59</v>
       </c>
       <c r="C110" s="43" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D110" s="44" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E110" s="44" t="s">
         <v>57</v>
@@ -6199,8 +6219,8 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J110" s="44" t="s">
-        <v>134</v>
+      <c r="J110" s="82" t="s">
+        <v>517</v>
       </c>
       <c r="K110" s="47"/>
     </row>
@@ -6212,10 +6232,10 @@
         <v>59</v>
       </c>
       <c r="C111" s="43" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D111" s="44" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="E111" s="44" t="s">
         <v>70</v>
@@ -6233,11 +6253,11 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J111" s="44" t="s">
-        <v>103</v>
+      <c r="J111" s="82" t="s">
+        <v>518</v>
       </c>
       <c r="K111" s="47" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -6248,10 +6268,10 @@
         <v>59</v>
       </c>
       <c r="C112" s="43" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D112" s="44" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E112" s="44" t="s">
         <v>70</v>
@@ -6269,11 +6289,11 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J112" s="44" t="s">
-        <v>103</v>
+      <c r="J112" s="82" t="s">
+        <v>518</v>
       </c>
       <c r="K112" s="47" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -6320,7 +6340,7 @@
         <v>12</v>
       </c>
       <c r="B115" s="56" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C115" s="53"/>
       <c r="D115" s="53"/>
@@ -6337,7 +6357,7 @@
         <v>13</v>
       </c>
       <c r="B116" s="56" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C116" s="53"/>
       <c r="D116" s="53"/>
@@ -6357,10 +6377,10 @@
         <v>59</v>
       </c>
       <c r="C117" s="43" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="D117" s="44" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="E117" s="44" t="s">
         <v>57</v>
@@ -6378,8 +6398,8 @@
         <f t="shared" ref="I117:I125" si="18">H117-G117</f>
         <v>0</v>
       </c>
-      <c r="J117" s="44" t="s">
-        <v>270</v>
+      <c r="J117" s="82" t="s">
+        <v>263</v>
       </c>
       <c r="K117" s="47"/>
     </row>
@@ -6390,11 +6410,11 @@
       <c r="B118" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="C118" s="43" t="s">
-        <v>271</v>
+      <c r="C118" s="48" t="s">
+        <v>264</v>
       </c>
       <c r="D118" s="44" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E118" s="44" t="s">
         <v>60</v>
@@ -6412,8 +6432,8 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="J118" s="44" t="s">
-        <v>134</v>
+      <c r="J118" s="82" t="s">
+        <v>133</v>
       </c>
       <c r="K118" s="47"/>
     </row>
@@ -6425,10 +6445,10 @@
         <v>59</v>
       </c>
       <c r="C119" s="43" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="D119" s="44" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E119" s="44" t="s">
         <v>57</v>
@@ -6446,8 +6466,8 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="J119" s="44" t="s">
-        <v>134</v>
+      <c r="J119" s="82" t="s">
+        <v>133</v>
       </c>
       <c r="K119" s="47"/>
     </row>
@@ -6459,10 +6479,10 @@
         <v>59</v>
       </c>
       <c r="C120" s="43" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D120" s="44" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E120" s="44" t="s">
         <v>57</v>
@@ -6480,8 +6500,8 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="J120" s="44" t="s">
-        <v>134</v>
+      <c r="J120" s="82" t="s">
+        <v>518</v>
       </c>
       <c r="K120" s="47"/>
     </row>
@@ -6493,10 +6513,10 @@
         <v>59</v>
       </c>
       <c r="C121" s="48" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="D121" s="44" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="E121" s="39" t="s">
         <v>66</v>
@@ -6525,10 +6545,10 @@
         <v>59</v>
       </c>
       <c r="C122" s="43" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="D122" s="44" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="E122" s="44" t="s">
         <v>57</v>
@@ -6546,8 +6566,8 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="J122" s="44" t="s">
-        <v>134</v>
+      <c r="J122" s="82" t="s">
+        <v>133</v>
       </c>
       <c r="K122" s="47"/>
     </row>
@@ -6559,10 +6579,10 @@
         <v>59</v>
       </c>
       <c r="C123" s="43" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="D123" s="44" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="E123" s="44" t="s">
         <v>57</v>
@@ -6580,8 +6600,8 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="J123" s="44" t="s">
-        <v>281</v>
+      <c r="J123" s="82" t="s">
+        <v>274</v>
       </c>
       <c r="K123" s="47"/>
     </row>
@@ -6593,10 +6613,10 @@
         <v>59</v>
       </c>
       <c r="C124" s="43" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="D124" s="44" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="E124" s="44" t="s">
         <v>48</v>
@@ -6614,8 +6634,8 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="J124" s="44" t="s">
-        <v>139</v>
+      <c r="J124" s="82" t="s">
+        <v>138</v>
       </c>
       <c r="K124" s="47"/>
     </row>
@@ -6627,10 +6647,10 @@
         <v>59</v>
       </c>
       <c r="C125" s="43" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="D125" s="44" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E125" s="44" t="s">
         <v>68</v>
@@ -6648,8 +6668,8 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="J125" s="44" t="s">
-        <v>286</v>
+      <c r="J125" s="82" t="s">
+        <v>279</v>
       </c>
       <c r="K125" s="47"/>
     </row>
@@ -6697,7 +6717,7 @@
         <v>12</v>
       </c>
       <c r="B128" s="58" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C128" s="53"/>
       <c r="D128" s="53"/>
@@ -6714,7 +6734,7 @@
         <v>13</v>
       </c>
       <c r="B129" s="58" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="C129" s="53"/>
       <c r="D129" s="53"/>
@@ -6734,10 +6754,10 @@
         <v>59</v>
       </c>
       <c r="C130" s="43" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D130" s="44" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="E130" s="44" t="s">
         <v>66</v>
@@ -6755,8 +6775,8 @@
         <f t="shared" ref="I130:I136" si="20">H130-G130</f>
         <v>0</v>
       </c>
-      <c r="J130" s="44" t="s">
-        <v>291</v>
+      <c r="J130" s="82" t="s">
+        <v>284</v>
       </c>
       <c r="K130" s="47"/>
     </row>
@@ -6768,10 +6788,10 @@
         <v>59</v>
       </c>
       <c r="C131" s="43" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D131" s="44" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="E131" s="44" t="s">
         <v>54</v>
@@ -6800,10 +6820,10 @@
         <v>59</v>
       </c>
       <c r="C132" s="43" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D132" s="44" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="E132" s="44" t="s">
         <v>57</v>
@@ -6821,8 +6841,8 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J132" s="44" t="s">
-        <v>296</v>
+      <c r="J132" s="82" t="s">
+        <v>289</v>
       </c>
       <c r="K132" s="47"/>
     </row>
@@ -6834,10 +6854,10 @@
         <v>59</v>
       </c>
       <c r="C133" s="43" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="D133" s="44" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="E133" s="44" t="s">
         <v>57</v>
@@ -6855,8 +6875,8 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J133" s="44" t="s">
-        <v>296</v>
+      <c r="J133" s="82" t="s">
+        <v>289</v>
       </c>
       <c r="K133" s="47"/>
     </row>
@@ -6868,10 +6888,10 @@
         <v>59</v>
       </c>
       <c r="C134" s="43" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D134" s="44" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="E134" s="44" t="s">
         <v>54</v>
@@ -6889,8 +6909,8 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J134" s="44" t="s">
-        <v>301</v>
+      <c r="J134" s="82" t="s">
+        <v>294</v>
       </c>
       <c r="K134" s="47"/>
     </row>
@@ -6902,10 +6922,10 @@
         <v>59</v>
       </c>
       <c r="C135" s="43" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="D135" s="44" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E135" s="44" t="s">
         <v>54</v>
@@ -6923,8 +6943,8 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J135" s="44" t="s">
-        <v>304</v>
+      <c r="J135" s="82" t="s">
+        <v>297</v>
       </c>
       <c r="K135" s="47"/>
     </row>
@@ -6936,10 +6956,10 @@
         <v>59</v>
       </c>
       <c r="C136" s="43" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="D136" s="44" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E136" s="44" t="s">
         <v>54</v>
@@ -6957,8 +6977,8 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J136" s="44" t="s">
-        <v>304</v>
+      <c r="J136" s="82" t="s">
+        <v>297</v>
       </c>
       <c r="K136" s="47"/>
     </row>
@@ -7006,7 +7026,7 @@
         <v>12</v>
       </c>
       <c r="B139" s="60" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C139" s="53"/>
       <c r="D139" s="53"/>
@@ -7023,7 +7043,7 @@
         <v>13</v>
       </c>
       <c r="B140" s="60" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C140" s="53"/>
       <c r="D140" s="53"/>
@@ -7043,10 +7063,10 @@
         <v>59</v>
       </c>
       <c r="C141" s="43" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="D141" s="44" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E141" s="44" t="s">
         <v>60</v>
@@ -7064,8 +7084,8 @@
         <f t="shared" ref="I141:I149" si="22">H141-G141</f>
         <v>0</v>
       </c>
-      <c r="J141" s="44" t="s">
-        <v>304</v>
+      <c r="J141" s="82" t="s">
+        <v>297</v>
       </c>
       <c r="K141" s="47"/>
     </row>
@@ -7077,10 +7097,10 @@
         <v>59</v>
       </c>
       <c r="C142" s="43" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="D142" s="44" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E142" s="44" t="s">
         <v>57</v>
@@ -7098,8 +7118,8 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J142" s="44" t="s">
-        <v>291</v>
+      <c r="J142" s="82" t="s">
+        <v>284</v>
       </c>
       <c r="K142" s="47"/>
     </row>
@@ -7111,10 +7131,10 @@
         <v>59</v>
       </c>
       <c r="C143" s="43" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D143" s="44" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="E143" s="44" t="s">
         <v>54</v>
@@ -7132,8 +7152,8 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J143" s="44" t="s">
-        <v>314</v>
+      <c r="J143" s="82" t="s">
+        <v>307</v>
       </c>
       <c r="K143" s="47"/>
     </row>
@@ -7145,10 +7165,10 @@
         <v>59</v>
       </c>
       <c r="C144" s="43" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="D144" s="44" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E144" s="44" t="s">
         <v>60</v>
@@ -7166,11 +7186,11 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J144" s="44" t="s">
-        <v>134</v>
+      <c r="J144" s="82" t="s">
+        <v>133</v>
       </c>
       <c r="K144" s="47" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
     </row>
     <row r="145" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -7181,10 +7201,10 @@
         <v>59</v>
       </c>
       <c r="C145" s="48" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="D145" s="39" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="E145" s="39" t="s">
         <v>66</v>
@@ -7213,10 +7233,10 @@
         <v>59</v>
       </c>
       <c r="C146" s="43" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="D146" s="44" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="E146" s="44" t="s">
         <v>48</v>
@@ -7234,7 +7254,7 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J146" s="44" t="s">
+      <c r="J146" s="82" t="s">
         <v>103</v>
       </c>
       <c r="K146" s="47"/>
@@ -7247,10 +7267,10 @@
         <v>59</v>
       </c>
       <c r="C147" s="43" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D147" s="44" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="E147" s="44" t="s">
         <v>54</v>
@@ -7268,8 +7288,8 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J147" s="44" t="s">
-        <v>322</v>
+      <c r="J147" s="82" t="s">
+        <v>315</v>
       </c>
       <c r="K147" s="47"/>
     </row>
@@ -7281,10 +7301,10 @@
         <v>59</v>
       </c>
       <c r="C148" s="43" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="D148" s="44" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="E148" s="44" t="s">
         <v>54</v>
@@ -7302,8 +7322,8 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J148" s="44" t="s">
-        <v>325</v>
+      <c r="J148" s="82" t="s">
+        <v>318</v>
       </c>
       <c r="K148" s="47"/>
     </row>
@@ -7315,10 +7335,10 @@
         <v>59</v>
       </c>
       <c r="C149" s="43" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="D149" s="44" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="E149" s="44" t="s">
         <v>60</v>
@@ -7336,8 +7356,8 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J149" s="44" t="s">
-        <v>328</v>
+      <c r="J149" s="82" t="s">
+        <v>321</v>
       </c>
       <c r="K149" s="47"/>
     </row>
@@ -7385,7 +7405,7 @@
         <v>12</v>
       </c>
       <c r="B152" s="62" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C152" s="53"/>
       <c r="D152" s="53"/>
@@ -7402,7 +7422,7 @@
         <v>13</v>
       </c>
       <c r="B153" s="62" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C153" s="53"/>
       <c r="D153" s="53"/>
@@ -7422,10 +7442,10 @@
         <v>59</v>
       </c>
       <c r="C154" s="43" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D154" s="44" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E154" s="44" t="s">
         <v>54</v>
@@ -7443,8 +7463,8 @@
         <f t="shared" ref="I154:I160" si="24">H154-G154</f>
         <v>0</v>
       </c>
-      <c r="J154" s="44" t="s">
-        <v>332</v>
+      <c r="J154" s="82" t="s">
+        <v>325</v>
       </c>
       <c r="K154" s="24"/>
     </row>
@@ -7456,10 +7476,10 @@
         <v>59</v>
       </c>
       <c r="C155" s="43" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="D155" s="44" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="E155" s="44" t="s">
         <v>54</v>
@@ -7477,8 +7497,8 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="J155" s="44" t="s">
-        <v>203</v>
+      <c r="J155" s="82" t="s">
+        <v>199</v>
       </c>
       <c r="K155" s="24"/>
     </row>
@@ -7490,10 +7510,10 @@
         <v>59</v>
       </c>
       <c r="C156" s="43" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="D156" s="44" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="E156" s="44" t="s">
         <v>54</v>
@@ -7511,8 +7531,8 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="J156" s="44" t="s">
-        <v>206</v>
+      <c r="J156" s="82" t="s">
+        <v>202</v>
       </c>
       <c r="K156" s="24"/>
     </row>
@@ -7524,10 +7544,10 @@
         <v>59</v>
       </c>
       <c r="C157" s="43" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="D157" s="44" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="E157" s="44" t="s">
         <v>54</v>
@@ -7545,8 +7565,8 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="J157" s="44" t="s">
-        <v>197</v>
+      <c r="J157" s="82" t="s">
+        <v>193</v>
       </c>
       <c r="K157" s="24"/>
     </row>
@@ -7558,10 +7578,10 @@
         <v>59</v>
       </c>
       <c r="C158" s="43" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D158" s="44" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="E158" s="44" t="s">
         <v>60</v>
@@ -7590,10 +7610,10 @@
         <v>59</v>
       </c>
       <c r="C159" s="43" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D159" s="44" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="E159" s="44" t="s">
         <v>70</v>
@@ -7622,10 +7642,10 @@
         <v>59</v>
       </c>
       <c r="C160" s="43" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="D160" s="44" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="E160" s="44" t="s">
         <v>54</v>
@@ -7643,8 +7663,8 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="J160" s="44" t="s">
-        <v>200</v>
+      <c r="J160" s="82" t="s">
+        <v>196</v>
       </c>
       <c r="K160" s="24"/>
     </row>
@@ -7692,7 +7712,7 @@
         <v>12</v>
       </c>
       <c r="B163" s="73" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C163" s="53"/>
       <c r="D163" s="53"/>
@@ -7709,7 +7729,7 @@
         <v>13</v>
       </c>
       <c r="B164" s="73" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C164" s="53"/>
       <c r="D164" s="53"/>
@@ -7729,10 +7749,10 @@
         <v>59</v>
       </c>
       <c r="C165" s="43" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D165" s="44" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E165" s="44" t="s">
         <v>66</v>
@@ -7750,8 +7770,8 @@
         <f t="shared" ref="I165:I172" si="26">H165-G165</f>
         <v>0</v>
       </c>
-      <c r="J165" s="44" t="s">
-        <v>291</v>
+      <c r="J165" s="82" t="s">
+        <v>284</v>
       </c>
       <c r="K165" s="47"/>
     </row>
@@ -7763,10 +7783,10 @@
         <v>59</v>
       </c>
       <c r="C166" s="43" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D166" s="44" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="E166" s="44" t="s">
         <v>57</v>
@@ -7784,8 +7804,8 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="J166" s="44" t="s">
-        <v>296</v>
+      <c r="J166" s="82" t="s">
+        <v>289</v>
       </c>
       <c r="K166" s="47"/>
     </row>
@@ -7797,10 +7817,10 @@
         <v>59</v>
       </c>
       <c r="C167" s="43" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="D167" s="44" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="E167" s="44" t="s">
         <v>60</v>
@@ -7818,8 +7838,8 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="J167" s="44" t="s">
-        <v>352</v>
+      <c r="J167" s="82" t="s">
+        <v>345</v>
       </c>
       <c r="K167" s="47"/>
     </row>
@@ -7831,10 +7851,10 @@
         <v>59</v>
       </c>
       <c r="C168" s="43" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D168" s="44" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="E168" s="44" t="s">
         <v>57</v>
@@ -7852,11 +7872,11 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="J168" s="44" t="s">
-        <v>286</v>
+      <c r="J168" s="82" t="s">
+        <v>279</v>
       </c>
       <c r="K168" s="47" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
     <row r="169" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -7867,10 +7887,10 @@
         <v>59</v>
       </c>
       <c r="C169" s="43" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D169" s="44" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="E169" s="44" t="s">
         <v>57</v>
@@ -7888,8 +7908,8 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="J169" s="44" t="s">
-        <v>296</v>
+      <c r="J169" s="82" t="s">
+        <v>289</v>
       </c>
       <c r="K169" s="47"/>
     </row>
@@ -7901,10 +7921,10 @@
         <v>59</v>
       </c>
       <c r="C170" s="43" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D170" s="44" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="E170" s="44" t="s">
         <v>57</v>
@@ -7922,8 +7942,8 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="J170" s="44" t="s">
-        <v>296</v>
+      <c r="J170" s="82" t="s">
+        <v>289</v>
       </c>
       <c r="K170" s="47"/>
     </row>
@@ -7935,10 +7955,10 @@
         <v>59</v>
       </c>
       <c r="C171" s="43" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="D171" s="44" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="E171" s="44" t="s">
         <v>54</v>
@@ -7956,8 +7976,8 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="J171" s="44" t="s">
-        <v>361</v>
+      <c r="J171" s="82" t="s">
+        <v>354</v>
       </c>
       <c r="K171" s="47"/>
     </row>
@@ -7969,10 +7989,10 @@
         <v>59</v>
       </c>
       <c r="C172" s="43" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="D172" s="44" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E172" s="44" t="s">
         <v>57</v>
@@ -8037,7 +8057,7 @@
         <v>12</v>
       </c>
       <c r="B175" s="75" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C175" s="53"/>
       <c r="D175" s="53"/>
@@ -8054,7 +8074,7 @@
         <v>13</v>
       </c>
       <c r="B176" s="75" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="C176" s="53"/>
       <c r="D176" s="53"/>
@@ -8074,10 +8094,10 @@
         <v>59</v>
       </c>
       <c r="C177" s="43" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="D177" s="44" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="E177" s="44" t="s">
         <v>60</v>
@@ -8095,8 +8115,8 @@
         <f t="shared" ref="I177:I185" si="28">H177-G177</f>
         <v>0</v>
       </c>
-      <c r="J177" s="44" t="s">
-        <v>352</v>
+      <c r="J177" s="82" t="s">
+        <v>354</v>
       </c>
       <c r="K177" s="47"/>
     </row>
@@ -8108,10 +8128,10 @@
         <v>59</v>
       </c>
       <c r="C178" s="43" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="D178" s="44" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E178" s="44" t="s">
         <v>57</v>
@@ -8129,8 +8149,8 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="J178" s="44" t="s">
-        <v>134</v>
+      <c r="J178" s="82" t="s">
+        <v>133</v>
       </c>
       <c r="K178" s="47"/>
     </row>
@@ -8142,10 +8162,10 @@
         <v>59</v>
       </c>
       <c r="C179" s="43" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="D179" s="44" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="E179" s="44" t="s">
         <v>57</v>
@@ -8163,8 +8183,8 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="J179" s="44" t="s">
-        <v>372</v>
+      <c r="J179" s="82" t="s">
+        <v>365</v>
       </c>
       <c r="K179" s="47"/>
     </row>
@@ -8176,10 +8196,10 @@
         <v>59</v>
       </c>
       <c r="C180" s="43" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D180" s="44" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E180" s="44" t="s">
         <v>57</v>
@@ -8197,7 +8217,9 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="J180" s="44"/>
+      <c r="J180" s="82" t="s">
+        <v>519</v>
+      </c>
       <c r="K180" s="47"/>
     </row>
     <row r="181" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -8208,10 +8230,10 @@
         <v>59</v>
       </c>
       <c r="C181" s="43" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="D181" s="44" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="E181" s="44" t="s">
         <v>57</v>
@@ -8229,8 +8251,8 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="J181" s="44" t="s">
-        <v>377</v>
+      <c r="J181" s="82" t="s">
+        <v>370</v>
       </c>
       <c r="K181" s="47"/>
     </row>
@@ -8242,10 +8264,10 @@
         <v>59</v>
       </c>
       <c r="C182" s="43" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D182" s="44" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="E182" s="44" t="s">
         <v>60</v>
@@ -8263,8 +8285,8 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="J182" s="44" t="s">
-        <v>380</v>
+      <c r="J182" s="82" t="s">
+        <v>373</v>
       </c>
       <c r="K182" s="47"/>
     </row>
@@ -8276,10 +8298,10 @@
         <v>59</v>
       </c>
       <c r="C183" s="43" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="D183" s="44" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="E183" s="44" t="s">
         <v>70</v>
@@ -8297,8 +8319,8 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="J183" s="44" t="s">
-        <v>383</v>
+      <c r="J183" s="82" t="s">
+        <v>520</v>
       </c>
       <c r="K183" s="47"/>
     </row>
@@ -8310,10 +8332,10 @@
         <v>59</v>
       </c>
       <c r="C184" s="48" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="D184" s="39" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="E184" s="39" t="s">
         <v>66</v>
@@ -8342,10 +8364,10 @@
         <v>59</v>
       </c>
       <c r="C185" s="43" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="D185" s="44" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="E185" s="44" t="s">
         <v>68</v>
@@ -8363,8 +8385,8 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="J185" s="44" t="s">
-        <v>386</v>
+      <c r="J185" s="82" t="s">
+        <v>378</v>
       </c>
       <c r="K185" s="47"/>
     </row>
@@ -8412,7 +8434,7 @@
         <v>12</v>
       </c>
       <c r="B188" s="76" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="C188" s="51"/>
       <c r="D188" s="51"/>
@@ -8429,7 +8451,7 @@
         <v>13</v>
       </c>
       <c r="B189" s="78" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="C189" s="51"/>
       <c r="D189" s="51"/>
@@ -8449,10 +8471,10 @@
         <v>59</v>
       </c>
       <c r="C190" s="43" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="D190" s="44" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="E190" s="44" t="s">
         <v>48</v>
@@ -8470,7 +8492,9 @@
         <f t="shared" ref="I190:I198" si="30">H190-G190</f>
         <v>0</v>
       </c>
-      <c r="J190" s="44"/>
+      <c r="J190" s="82" t="s">
+        <v>521</v>
+      </c>
       <c r="K190" s="47"/>
     </row>
     <row r="191" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -8481,10 +8505,10 @@
         <v>59</v>
       </c>
       <c r="C191" s="43" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="D191" s="44" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="E191" s="44" t="s">
         <v>51</v>
@@ -8502,9 +8526,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="J191" s="39"/>
+      <c r="J191" s="82" t="s">
+        <v>521</v>
+      </c>
       <c r="K191" s="39" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
     </row>
     <row r="192" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -8515,10 +8541,10 @@
         <v>59</v>
       </c>
       <c r="C192" s="43" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="D192" s="44" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E192" s="44" t="s">
         <v>51</v>
@@ -8536,7 +8562,9 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="J192" s="44"/>
+      <c r="J192" s="82" t="s">
+        <v>521</v>
+      </c>
       <c r="K192" s="47"/>
     </row>
     <row r="193" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -8547,10 +8575,10 @@
         <v>59</v>
       </c>
       <c r="C193" s="43" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="D193" s="44" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E193" s="44" t="s">
         <v>51</v>
@@ -8568,7 +8596,9 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="J193" s="44"/>
+      <c r="J193" s="82" t="s">
+        <v>521</v>
+      </c>
       <c r="K193" s="47"/>
     </row>
     <row r="194" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -8579,10 +8609,10 @@
         <v>59</v>
       </c>
       <c r="C194" s="43" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="D194" s="44" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="E194" s="44" t="s">
         <v>57</v>
@@ -8600,8 +8630,8 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="J194" s="44" t="s">
-        <v>134</v>
+      <c r="J194" s="82" t="s">
+        <v>522</v>
       </c>
       <c r="K194" s="47"/>
     </row>
@@ -8613,10 +8643,10 @@
         <v>59</v>
       </c>
       <c r="C195" s="43" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="D195" s="44" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="E195" s="44" t="s">
         <v>57</v>
@@ -8634,9 +8664,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="J195" s="44"/>
+      <c r="J195" s="82" t="s">
+        <v>522</v>
+      </c>
       <c r="K195" s="47" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
     </row>
     <row r="196" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -8647,10 +8679,10 @@
         <v>59</v>
       </c>
       <c r="C196" s="48" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="D196" s="44" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="E196" s="39" t="s">
         <v>66</v>
@@ -8670,7 +8702,7 @@
       </c>
       <c r="J196" s="44"/>
       <c r="K196" s="47" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
     </row>
     <row r="197" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -8681,10 +8713,10 @@
         <v>59</v>
       </c>
       <c r="C197" s="43" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D197" s="44" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="E197" s="44" t="s">
         <v>54</v>
@@ -8702,8 +8734,8 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="J197" s="44" t="s">
-        <v>206</v>
+      <c r="J197" s="82" t="s">
+        <v>202</v>
       </c>
       <c r="K197" s="47"/>
     </row>
@@ -8715,10 +8747,10 @@
         <v>59</v>
       </c>
       <c r="C198" s="43" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="D198" s="44" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="E198" s="44" t="s">
         <v>57</v>
@@ -8736,8 +8768,8 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="J198" s="44" t="s">
-        <v>155</v>
+      <c r="J198" s="82" t="s">
+        <v>154</v>
       </c>
       <c r="K198" s="47"/>
     </row>
@@ -8767,7 +8799,7 @@
     </row>
     <row r="200" spans="1:11" s="42" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="74" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="B200" s="53"/>
       <c r="C200" s="53"/>
@@ -8785,7 +8817,7 @@
         <v>12</v>
       </c>
       <c r="B201" s="75" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C201" s="53"/>
       <c r="D201" s="53"/>
@@ -8802,7 +8834,7 @@
         <v>13</v>
       </c>
       <c r="B202" s="75" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C202" s="53"/>
       <c r="D202" s="53"/>
@@ -8822,10 +8854,10 @@
         <v>59</v>
       </c>
       <c r="C203" s="43" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="D203" s="44" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="E203" s="44" t="s">
         <v>51</v>
@@ -8843,9 +8875,11 @@
         <f t="shared" ref="I203:I210" si="32">H203-G203</f>
         <v>0</v>
       </c>
-      <c r="J203" s="44"/>
+      <c r="J203" s="82" t="s">
+        <v>521</v>
+      </c>
       <c r="K203" s="39" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
     </row>
     <row r="204" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -8856,10 +8890,10 @@
         <v>59</v>
       </c>
       <c r="C204" s="43" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="D204" s="44" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E204" s="44" t="s">
         <v>51</v>
@@ -8877,7 +8911,9 @@
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="J204" s="44"/>
+      <c r="J204" s="82" t="s">
+        <v>521</v>
+      </c>
       <c r="K204" s="47"/>
     </row>
     <row r="205" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -8888,10 +8924,10 @@
         <v>59</v>
       </c>
       <c r="C205" s="43" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="D205" s="44" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E205" s="44" t="s">
         <v>51</v>
@@ -8909,7 +8945,9 @@
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="J205" s="44"/>
+      <c r="J205" s="82" t="s">
+        <v>521</v>
+      </c>
       <c r="K205" s="47"/>
     </row>
     <row r="206" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -8920,10 +8958,10 @@
         <v>59</v>
       </c>
       <c r="C206" s="43" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="D206" s="44" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="E206" s="44" t="s">
         <v>57</v>
@@ -8941,8 +8979,8 @@
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="J206" s="44" t="s">
-        <v>417</v>
+      <c r="J206" s="82" t="s">
+        <v>524</v>
       </c>
       <c r="K206" s="47"/>
     </row>
@@ -8954,10 +8992,10 @@
         <v>59</v>
       </c>
       <c r="C207" s="43" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="D207" s="44" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="E207" s="44" t="s">
         <v>57</v>
@@ -8975,8 +9013,8 @@
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="J207" s="44" t="s">
-        <v>420</v>
+      <c r="J207" s="82" t="s">
+        <v>522</v>
       </c>
       <c r="K207" s="47"/>
     </row>
@@ -8988,10 +9026,10 @@
         <v>59</v>
       </c>
       <c r="C208" s="43" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="D208" s="44" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="E208" s="44" t="s">
         <v>60</v>
@@ -9020,10 +9058,10 @@
         <v>59</v>
       </c>
       <c r="C209" s="43" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="D209" s="44" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="E209" s="44" t="s">
         <v>54</v>
@@ -9041,8 +9079,8 @@
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="J209" s="44" t="s">
-        <v>425</v>
+      <c r="J209" s="82" t="s">
+        <v>525</v>
       </c>
       <c r="K209" s="47"/>
     </row>
@@ -9054,7 +9092,7 @@
         <v>59</v>
       </c>
       <c r="C210" s="43" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="D210" s="44" t="s">
         <v>116</v>
@@ -9075,8 +9113,8 @@
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="J210" s="44" t="s">
-        <v>427</v>
+      <c r="J210" s="82" t="s">
+        <v>416</v>
       </c>
       <c r="K210" s="47"/>
     </row>
@@ -9106,7 +9144,7 @@
     </row>
     <row r="212" spans="1:11" s="42" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="72" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="B212" s="53"/>
       <c r="C212" s="53"/>
@@ -9124,7 +9162,7 @@
         <v>12</v>
       </c>
       <c r="B213" s="73" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="C213" s="53"/>
       <c r="D213" s="53"/>
@@ -9141,7 +9179,7 @@
         <v>13</v>
       </c>
       <c r="B214" s="73" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="C214" s="53"/>
       <c r="D214" s="53"/>
@@ -9161,10 +9199,10 @@
         <v>59</v>
       </c>
       <c r="C215" s="43" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="D215" s="44" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="E215" s="44" t="s">
         <v>68</v>
@@ -9182,8 +9220,8 @@
         <f t="shared" ref="I215:I223" si="34">H215-G215</f>
         <v>0</v>
       </c>
-      <c r="J215" s="44" t="s">
-        <v>432</v>
+      <c r="J215" s="82" t="s">
+        <v>421</v>
       </c>
       <c r="K215" s="47"/>
     </row>
@@ -9195,10 +9233,10 @@
         <v>59</v>
       </c>
       <c r="C216" s="43" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="D216" s="44" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="E216" s="44" t="s">
         <v>48</v>
@@ -9216,8 +9254,8 @@
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="J216" s="44" t="s">
-        <v>435</v>
+      <c r="J216" s="82" t="s">
+        <v>424</v>
       </c>
       <c r="K216" s="47"/>
     </row>
@@ -9229,10 +9267,10 @@
         <v>59</v>
       </c>
       <c r="C217" s="43" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="D217" s="44" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="E217" s="44" t="s">
         <v>68</v>
@@ -9250,8 +9288,8 @@
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="J217" s="44" t="s">
-        <v>438</v>
+      <c r="J217" s="82" t="s">
+        <v>427</v>
       </c>
       <c r="K217" s="47"/>
     </row>
@@ -9263,10 +9301,10 @@
         <v>59</v>
       </c>
       <c r="C218" s="43" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="D218" s="44" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="E218" s="44" t="s">
         <v>68</v>
@@ -9284,8 +9322,8 @@
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="J218" s="44" t="s">
-        <v>441</v>
+      <c r="J218" s="82" t="s">
+        <v>430</v>
       </c>
       <c r="K218" s="47"/>
     </row>
@@ -9297,10 +9335,10 @@
         <v>59</v>
       </c>
       <c r="C219" s="43" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="D219" s="44" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="E219" s="44" t="s">
         <v>68</v>
@@ -9318,8 +9356,8 @@
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="J219" s="44" t="s">
-        <v>441</v>
+      <c r="J219" s="82" t="s">
+        <v>430</v>
       </c>
       <c r="K219" s="47"/>
     </row>
@@ -9331,10 +9369,10 @@
         <v>59</v>
       </c>
       <c r="C220" s="43" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="D220" s="44" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="E220" s="44" t="s">
         <v>68</v>
@@ -9352,8 +9390,8 @@
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="J220" s="44" t="s">
-        <v>446</v>
+      <c r="J220" s="82" t="s">
+        <v>435</v>
       </c>
       <c r="K220" s="47"/>
     </row>
@@ -9365,10 +9403,10 @@
         <v>59</v>
       </c>
       <c r="C221" s="48" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="D221" s="39" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="E221" s="39" t="s">
         <v>66</v>
@@ -9388,7 +9426,7 @@
       </c>
       <c r="J221" s="44"/>
       <c r="K221" s="47" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
     </row>
     <row r="222" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -9398,11 +9436,11 @@
       <c r="B222" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="C222" s="43" t="s">
-        <v>447</v>
+      <c r="C222" s="48" t="s">
+        <v>436</v>
       </c>
       <c r="D222" s="44" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="E222" s="44" t="s">
         <v>48</v>
@@ -9420,8 +9458,8 @@
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="J222" s="44" t="s">
-        <v>449</v>
+      <c r="J222" s="82" t="s">
+        <v>438</v>
       </c>
       <c r="K222" s="47"/>
     </row>
@@ -9433,10 +9471,10 @@
         <v>59</v>
       </c>
       <c r="C223" s="43" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="D223" s="44" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="E223" s="44" t="s">
         <v>60</v>
@@ -9483,7 +9521,7 @@
     </row>
     <row r="225" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A225" s="65" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B225" s="53"/>
       <c r="C225" s="53"/>
@@ -9501,7 +9539,7 @@
         <v>12</v>
       </c>
       <c r="B226" s="76" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C226" s="51"/>
       <c r="D226" s="51"/>
@@ -9518,7 +9556,7 @@
         <v>13</v>
       </c>
       <c r="B227" s="78" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="C227" s="51"/>
       <c r="D227" s="51"/>
@@ -9538,10 +9576,10 @@
         <v>59</v>
       </c>
       <c r="C228" s="43" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="D228" s="44" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="E228" s="44" t="s">
         <v>68</v>
@@ -9559,8 +9597,8 @@
         <f t="shared" ref="I228:I236" si="36">H228-G228</f>
         <v>0</v>
       </c>
-      <c r="J228" s="44" t="s">
-        <v>456</v>
+      <c r="J228" s="82" t="s">
+        <v>445</v>
       </c>
       <c r="K228" s="47"/>
     </row>
@@ -9572,10 +9610,10 @@
         <v>59</v>
       </c>
       <c r="C229" s="43" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="D229" s="44" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="E229" s="44" t="s">
         <v>68</v>
@@ -9593,8 +9631,8 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="J229" s="44" t="s">
-        <v>459</v>
+      <c r="J229" s="82" t="s">
+        <v>448</v>
       </c>
       <c r="K229" s="47"/>
     </row>
@@ -9606,10 +9644,10 @@
         <v>59</v>
       </c>
       <c r="C230" s="43" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="D230" s="44" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="E230" s="44" t="s">
         <v>68</v>
@@ -9627,8 +9665,8 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="J230" s="44" t="s">
-        <v>462</v>
+      <c r="J230" s="82" t="s">
+        <v>451</v>
       </c>
       <c r="K230" s="47"/>
     </row>
@@ -9640,10 +9678,10 @@
         <v>59</v>
       </c>
       <c r="C231" s="43" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="D231" s="44" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="E231" s="44" t="s">
         <v>68</v>
@@ -9661,8 +9699,8 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="J231" s="44" t="s">
-        <v>462</v>
+      <c r="J231" s="82" t="s">
+        <v>451</v>
       </c>
       <c r="K231" s="47"/>
     </row>
@@ -9674,10 +9712,10 @@
         <v>59</v>
       </c>
       <c r="C232" s="43" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="D232" s="44" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="E232" s="44" t="s">
         <v>68</v>
@@ -9695,8 +9733,8 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="J232" s="44" t="s">
-        <v>467</v>
+      <c r="J232" s="82" t="s">
+        <v>456</v>
       </c>
       <c r="K232" s="47"/>
     </row>
@@ -9708,10 +9746,10 @@
         <v>59</v>
       </c>
       <c r="C233" s="43" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="D233" s="44" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="E233" s="44" t="s">
         <v>68</v>
@@ -9729,8 +9767,8 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="J233" s="44" t="s">
-        <v>470</v>
+      <c r="J233" s="82" t="s">
+        <v>459</v>
       </c>
       <c r="K233" s="47"/>
     </row>
@@ -9742,10 +9780,10 @@
         <v>59</v>
       </c>
       <c r="C234" s="48" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="D234" s="39" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="E234" s="39" t="s">
         <v>66</v>
@@ -9765,7 +9803,7 @@
       </c>
       <c r="J234" s="44"/>
       <c r="K234" s="47" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -9776,10 +9814,10 @@
         <v>59</v>
       </c>
       <c r="C235" s="43" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="D235" s="44" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="E235" s="44" t="s">
         <v>68</v>
@@ -9797,8 +9835,8 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="J235" s="44" t="s">
-        <v>473</v>
+      <c r="J235" s="82" t="s">
+        <v>462</v>
       </c>
       <c r="K235" s="47"/>
     </row>
@@ -9810,10 +9848,10 @@
         <v>59</v>
       </c>
       <c r="C236" s="43" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="D236" s="44" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="E236" s="44" t="s">
         <v>60</v>
@@ -9860,7 +9898,7 @@
     </row>
     <row r="238" spans="1:11" s="42" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="74" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="B238" s="53"/>
       <c r="C238" s="53"/>
@@ -9878,7 +9916,7 @@
         <v>12</v>
       </c>
       <c r="B239" s="75" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="C239" s="53"/>
       <c r="D239" s="53"/>
@@ -9895,7 +9933,7 @@
         <v>13</v>
       </c>
       <c r="B240" s="75" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="C240" s="53"/>
       <c r="D240" s="53"/>
@@ -9915,10 +9953,10 @@
         <v>59</v>
       </c>
       <c r="C241" s="43" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="D241" s="44" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="E241" s="44" t="s">
         <v>68</v>
@@ -9936,8 +9974,8 @@
         <f t="shared" ref="I241:I251" si="38">H241-G241</f>
         <v>0</v>
       </c>
-      <c r="J241" s="44" t="s">
-        <v>480</v>
+      <c r="J241" s="82" t="s">
+        <v>469</v>
       </c>
       <c r="K241" s="47"/>
     </row>
@@ -9949,10 +9987,10 @@
         <v>59</v>
       </c>
       <c r="C242" s="43" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="D242" s="44" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="E242" s="44" t="s">
         <v>68</v>
@@ -9970,8 +10008,8 @@
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="J242" s="44" t="s">
-        <v>480</v>
+      <c r="J242" s="82" t="s">
+        <v>469</v>
       </c>
       <c r="K242" s="47"/>
     </row>
@@ -9983,10 +10021,10 @@
         <v>59</v>
       </c>
       <c r="C243" s="43" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="D243" s="44" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="E243" s="44" t="s">
         <v>68</v>
@@ -10004,8 +10042,8 @@
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="J243" s="44" t="s">
-        <v>480</v>
+      <c r="J243" s="82" t="s">
+        <v>469</v>
       </c>
       <c r="K243" s="47"/>
     </row>
@@ -10017,10 +10055,10 @@
         <v>59</v>
       </c>
       <c r="C244" s="43" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D244" s="44" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="E244" s="44" t="s">
         <v>68</v>
@@ -10038,8 +10076,8 @@
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="J244" s="44" t="s">
-        <v>480</v>
+      <c r="J244" s="82" t="s">
+        <v>469</v>
       </c>
       <c r="K244" s="47"/>
     </row>
@@ -10051,10 +10089,10 @@
         <v>59</v>
       </c>
       <c r="C245" s="43" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="D245" s="44" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="E245" s="44" t="s">
         <v>68</v>
@@ -10083,10 +10121,10 @@
         <v>59</v>
       </c>
       <c r="C246" s="43" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="D246" s="44" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="E246" s="44" t="s">
         <v>68</v>
@@ -10104,8 +10142,8 @@
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="J246" s="44" t="s">
-        <v>480</v>
+      <c r="J246" s="82" t="s">
+        <v>469</v>
       </c>
       <c r="K246" s="47"/>
     </row>
@@ -10117,10 +10155,10 @@
         <v>59</v>
       </c>
       <c r="C247" s="43" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="D247" s="44" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="E247" s="44" t="s">
         <v>68</v>
@@ -10149,10 +10187,10 @@
         <v>59</v>
       </c>
       <c r="C248" s="43" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="D248" s="44" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="E248" s="44" t="s">
         <v>68</v>
@@ -10181,10 +10219,10 @@
         <v>59</v>
       </c>
       <c r="C249" s="43" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="D249" s="44" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="E249" s="44" t="s">
         <v>68</v>
@@ -10213,10 +10251,10 @@
         <v>59</v>
       </c>
       <c r="C250" s="48" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="D250" s="39" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="E250" s="39" t="s">
         <v>66</v>
@@ -10236,7 +10274,7 @@
       </c>
       <c r="J250" s="44"/>
       <c r="K250" s="47" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
     </row>
     <row r="251" spans="1:11" s="42" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -10247,10 +10285,10 @@
         <v>59</v>
       </c>
       <c r="C251" s="43" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="D251" s="44" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="E251" s="44" t="s">
         <v>60</v>
@@ -10689,9 +10727,132 @@
     <hyperlink ref="J32" r:id="rId15"/>
     <hyperlink ref="J33" r:id="rId16"/>
     <hyperlink ref="J34" r:id="rId17"/>
+    <hyperlink ref="J37" r:id="rId18"/>
+    <hyperlink ref="J42" r:id="rId19"/>
+    <hyperlink ref="J43" r:id="rId20"/>
+    <hyperlink ref="J49" r:id="rId21"/>
+    <hyperlink ref="J48" r:id="rId22"/>
+    <hyperlink ref="J47" r:id="rId23"/>
+    <hyperlink ref="J44" r:id="rId24"/>
+    <hyperlink ref="J45" r:id="rId25"/>
+    <hyperlink ref="J50" r:id="rId26"/>
+    <hyperlink ref="J55" r:id="rId27"/>
+    <hyperlink ref="J56" r:id="rId28"/>
+    <hyperlink ref="J57" r:id="rId29"/>
+    <hyperlink ref="J58" r:id="rId30"/>
+    <hyperlink ref="J59" r:id="rId31"/>
+    <hyperlink ref="J60" r:id="rId32"/>
+    <hyperlink ref="J62" r:id="rId33"/>
+    <hyperlink ref="J67" r:id="rId34"/>
+    <hyperlink ref="J68" r:id="rId35"/>
+    <hyperlink ref="J69" r:id="rId36"/>
+    <hyperlink ref="J70" r:id="rId37"/>
+    <hyperlink ref="J72" r:id="rId38"/>
+    <hyperlink ref="J73" r:id="rId39"/>
+    <hyperlink ref="J74" r:id="rId40"/>
+    <hyperlink ref="J75" r:id="rId41"/>
+    <hyperlink ref="J80" r:id="rId42"/>
+    <hyperlink ref="J81" r:id="rId43"/>
+    <hyperlink ref="J82" r:id="rId44"/>
+    <hyperlink ref="J83" r:id="rId45"/>
+    <hyperlink ref="J84" r:id="rId46"/>
+    <hyperlink ref="J85" r:id="rId47"/>
+    <hyperlink ref="J86" r:id="rId48"/>
+    <hyperlink ref="J87" r:id="rId49"/>
+    <hyperlink ref="J96" r:id="rId50"/>
+    <hyperlink ref="J98" r:id="rId51"/>
+    <hyperlink ref="J92" r:id="rId52"/>
+    <hyperlink ref="J93" r:id="rId53"/>
+    <hyperlink ref="J94" r:id="rId54"/>
+    <hyperlink ref="J95" r:id="rId55"/>
+    <hyperlink ref="J97" r:id="rId56"/>
+    <hyperlink ref="J105" r:id="rId57"/>
+    <hyperlink ref="J106" r:id="rId58"/>
+    <hyperlink ref="J107" r:id="rId59"/>
+    <hyperlink ref="J108" r:id="rId60"/>
+    <hyperlink ref="J109" r:id="rId61"/>
+    <hyperlink ref="J110" r:id="rId62"/>
+    <hyperlink ref="J111" r:id="rId63"/>
+    <hyperlink ref="J112" r:id="rId64"/>
+    <hyperlink ref="J117" r:id="rId65"/>
+    <hyperlink ref="J118" r:id="rId66"/>
+    <hyperlink ref="J119" r:id="rId67"/>
+    <hyperlink ref="J120" r:id="rId68"/>
+    <hyperlink ref="J122" r:id="rId69"/>
+    <hyperlink ref="J123" r:id="rId70"/>
+    <hyperlink ref="J124" r:id="rId71"/>
+    <hyperlink ref="J125" r:id="rId72"/>
+    <hyperlink ref="J130" r:id="rId73"/>
+    <hyperlink ref="J132" r:id="rId74"/>
+    <hyperlink ref="J133" r:id="rId75"/>
+    <hyperlink ref="J134" r:id="rId76"/>
+    <hyperlink ref="J135" r:id="rId77"/>
+    <hyperlink ref="J136" r:id="rId78"/>
+    <hyperlink ref="J141" r:id="rId79"/>
+    <hyperlink ref="J142" r:id="rId80"/>
+    <hyperlink ref="J143" r:id="rId81"/>
+    <hyperlink ref="J144" r:id="rId82"/>
+    <hyperlink ref="J146" r:id="rId83"/>
+    <hyperlink ref="J147" r:id="rId84"/>
+    <hyperlink ref="J148" r:id="rId85"/>
+    <hyperlink ref="J149" r:id="rId86"/>
+    <hyperlink ref="J154" r:id="rId87"/>
+    <hyperlink ref="J155" r:id="rId88"/>
+    <hyperlink ref="J156" r:id="rId89"/>
+    <hyperlink ref="J157" r:id="rId90"/>
+    <hyperlink ref="J160" r:id="rId91"/>
+    <hyperlink ref="J165" r:id="rId92"/>
+    <hyperlink ref="J166" r:id="rId93"/>
+    <hyperlink ref="J167" r:id="rId94"/>
+    <hyperlink ref="J168" r:id="rId95"/>
+    <hyperlink ref="J169" r:id="rId96"/>
+    <hyperlink ref="J170" r:id="rId97"/>
+    <hyperlink ref="J171" r:id="rId98"/>
+    <hyperlink ref="J177" r:id="rId99"/>
+    <hyperlink ref="J178" r:id="rId100"/>
+    <hyperlink ref="J179" r:id="rId101"/>
+    <hyperlink ref="J182" r:id="rId102"/>
+    <hyperlink ref="J181" r:id="rId103"/>
+    <hyperlink ref="J180" r:id="rId104"/>
+    <hyperlink ref="J183" r:id="rId105"/>
+    <hyperlink ref="J185" r:id="rId106"/>
+    <hyperlink ref="J190" r:id="rId107"/>
+    <hyperlink ref="J191" r:id="rId108"/>
+    <hyperlink ref="J192" r:id="rId109"/>
+    <hyperlink ref="J193" r:id="rId110"/>
+    <hyperlink ref="J194" r:id="rId111"/>
+    <hyperlink ref="J195" r:id="rId112"/>
+    <hyperlink ref="J197" r:id="rId113"/>
+    <hyperlink ref="J198" r:id="rId114"/>
+    <hyperlink ref="J203" r:id="rId115"/>
+    <hyperlink ref="J204" r:id="rId116"/>
+    <hyperlink ref="J205" r:id="rId117"/>
+    <hyperlink ref="J206" r:id="rId118"/>
+    <hyperlink ref="J207" r:id="rId119"/>
+    <hyperlink ref="J209" r:id="rId120"/>
+    <hyperlink ref="J210" r:id="rId121"/>
+    <hyperlink ref="J215" r:id="rId122"/>
+    <hyperlink ref="J216" r:id="rId123"/>
+    <hyperlink ref="J217" r:id="rId124"/>
+    <hyperlink ref="J218" r:id="rId125"/>
+    <hyperlink ref="J219" r:id="rId126"/>
+    <hyperlink ref="J220" r:id="rId127"/>
+    <hyperlink ref="J222" r:id="rId128"/>
+    <hyperlink ref="J228" r:id="rId129"/>
+    <hyperlink ref="J230" r:id="rId130"/>
+    <hyperlink ref="J231" r:id="rId131"/>
+    <hyperlink ref="J232" r:id="rId132"/>
+    <hyperlink ref="J233" r:id="rId133"/>
+    <hyperlink ref="J235" r:id="rId134"/>
+    <hyperlink ref="J241" r:id="rId135"/>
+    <hyperlink ref="J242" r:id="rId136"/>
+    <hyperlink ref="J243" r:id="rId137"/>
+    <hyperlink ref="J244" r:id="rId138"/>
+    <hyperlink ref="J246" r:id="rId139"/>
+    <hyperlink ref="J229" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId18"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId141"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
